--- a/output/Daily_Route_Summary_compact.xlsx
+++ b/output/Daily_Route_Summary_compact.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,40 +424,35 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>driver_label</t>
+          <t>day</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>day</t>
+          <t>stop_count</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>stop_count</t>
+          <t>service_min</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>service_min</t>
+          <t>drive_min</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>drive_min</t>
+          <t>dist_km</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>dist_km</t>
+          <t>total_min</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
-        <is>
-          <t>total_min</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>overtime_min</t>
         </is>
@@ -469,31 +464,26 @@
           <t>P01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>P01｜平鎮1</t>
-        </is>
+      <c r="B2" t="n">
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>473</v>
       </c>
       <c r="E2" t="n">
-        <v>331</v>
+        <v>325.88</v>
       </c>
       <c r="F2" t="n">
-        <v>204.13</v>
+        <v>190.1</v>
       </c>
       <c r="G2" t="n">
-        <v>119.08</v>
+        <v>798.88</v>
       </c>
       <c r="H2" t="n">
-        <v>535.13</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
+        <v>258.88</v>
       </c>
     </row>
     <row r="3">
@@ -502,31 +492,26 @@
           <t>P01</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>P01｜平鎮1</t>
-        </is>
+      <c r="B3" t="n">
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>400</v>
       </c>
       <c r="E3" t="n">
-        <v>264</v>
+        <v>323.02</v>
       </c>
       <c r="F3" t="n">
-        <v>271.93</v>
+        <v>188.43</v>
       </c>
       <c r="G3" t="n">
-        <v>158.62</v>
+        <v>723.02</v>
       </c>
       <c r="H3" t="n">
-        <v>535.9299999999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
+        <v>183.02</v>
       </c>
     </row>
     <row r="4">
@@ -535,31 +520,26 @@
           <t>P01</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>P01｜平鎮1</t>
-        </is>
+      <c r="B4" t="n">
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>388</v>
       </c>
       <c r="E4" t="n">
-        <v>287</v>
+        <v>384.5</v>
       </c>
       <c r="F4" t="n">
-        <v>246.51</v>
+        <v>224.29</v>
       </c>
       <c r="G4" t="n">
-        <v>143.79</v>
+        <v>772.5</v>
       </c>
       <c r="H4" t="n">
-        <v>533.51</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
+        <v>232.5</v>
       </c>
     </row>
     <row r="5">
@@ -568,31 +548,26 @@
           <t>P01</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>P01｜平鎮1</t>
-        </is>
+      <c r="B5" t="n">
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>428</v>
       </c>
       <c r="E5" t="n">
-        <v>256</v>
+        <v>384.52</v>
       </c>
       <c r="F5" t="n">
-        <v>283.74</v>
+        <v>224.3</v>
       </c>
       <c r="G5" t="n">
-        <v>165.51</v>
+        <v>812.52</v>
       </c>
       <c r="H5" t="n">
-        <v>539.74</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
+        <v>272.52</v>
       </c>
     </row>
     <row r="6">
@@ -601,31 +576,26 @@
           <t>P01</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>P01｜平鎮1</t>
-        </is>
+      <c r="B6" t="n">
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>23</v>
+        <v>450</v>
       </c>
       <c r="E6" t="n">
-        <v>316</v>
+        <v>345.14</v>
       </c>
       <c r="F6" t="n">
-        <v>218.1</v>
+        <v>201.33</v>
       </c>
       <c r="G6" t="n">
-        <v>127.23</v>
+        <v>795.14</v>
       </c>
       <c r="H6" t="n">
-        <v>534.1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
+        <v>255.14</v>
       </c>
     </row>
     <row r="7">
@@ -634,31 +604,26 @@
           <t>P01</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>P01｜平鎮1</t>
-        </is>
+      <c r="B7" t="n">
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>351</v>
       </c>
       <c r="E7" t="n">
-        <v>256</v>
+        <v>388.55</v>
       </c>
       <c r="F7" t="n">
-        <v>282.36</v>
+        <v>226.65</v>
       </c>
       <c r="G7" t="n">
-        <v>164.71</v>
+        <v>739.55</v>
       </c>
       <c r="H7" t="n">
-        <v>538.36</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
+        <v>199.55</v>
       </c>
     </row>
     <row r="8">
@@ -667,31 +632,26 @@
           <t>P02</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>P02｜平鎮2</t>
-        </is>
+      <c r="B8" t="n">
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>439</v>
       </c>
       <c r="E8" t="n">
-        <v>240</v>
+        <v>364.99</v>
       </c>
       <c r="F8" t="n">
-        <v>298.6</v>
+        <v>212.91</v>
       </c>
       <c r="G8" t="n">
-        <v>174.18</v>
+        <v>803.99</v>
       </c>
       <c r="H8" t="n">
-        <v>538.6</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
+        <v>263.99</v>
       </c>
     </row>
     <row r="9">
@@ -700,31 +660,26 @@
           <t>P02</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>P02｜平鎮2</t>
-        </is>
+      <c r="B9" t="n">
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>22</v>
+        <v>376</v>
       </c>
       <c r="E9" t="n">
-        <v>288</v>
+        <v>435.71</v>
       </c>
       <c r="F9" t="n">
-        <v>251.43</v>
+        <v>254.16</v>
       </c>
       <c r="G9" t="n">
-        <v>146.67</v>
+        <v>811.71</v>
       </c>
       <c r="H9" t="n">
-        <v>539.4299999999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
+        <v>271.71</v>
       </c>
     </row>
     <row r="10">
@@ -733,31 +688,26 @@
           <t>P02</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>P02｜平鎮2</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>21</v>
+        <v>344</v>
       </c>
       <c r="E10" t="n">
-        <v>272</v>
+        <v>392.93</v>
       </c>
       <c r="F10" t="n">
-        <v>264.67</v>
+        <v>229.21</v>
       </c>
       <c r="G10" t="n">
-        <v>154.39</v>
+        <v>736.9299999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>536.67</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
+        <v>196.93</v>
       </c>
     </row>
     <row r="11">
@@ -766,31 +716,26 @@
           <t>P02</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>P02｜平鎮2</t>
-        </is>
+      <c r="B11" t="n">
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="D11" t="n">
-        <v>23</v>
+        <v>436</v>
       </c>
       <c r="E11" t="n">
-        <v>288</v>
+        <v>382.15</v>
       </c>
       <c r="F11" t="n">
-        <v>251.89</v>
+        <v>222.92</v>
       </c>
       <c r="G11" t="n">
-        <v>146.94</v>
+        <v>818.15</v>
       </c>
       <c r="H11" t="n">
-        <v>539.89</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
+        <v>278.15</v>
       </c>
     </row>
     <row r="12">
@@ -799,31 +744,26 @@
           <t>P02</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>P02｜平鎮2</t>
-        </is>
+      <c r="B12" t="n">
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>19</v>
+        <v>364</v>
       </c>
       <c r="E12" t="n">
-        <v>267.5</v>
+        <v>355.94</v>
       </c>
       <c r="F12" t="n">
-        <v>266.45</v>
+        <v>207.63</v>
       </c>
       <c r="G12" t="n">
-        <v>155.43</v>
+        <v>719.9400000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>533.95</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
+        <v>179.94</v>
       </c>
     </row>
     <row r="13">
@@ -832,31 +772,26 @@
           <t>P02</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>P02｜平鎮2</t>
-        </is>
+      <c r="B13" t="n">
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D13" t="n">
-        <v>23</v>
+        <v>368</v>
       </c>
       <c r="E13" t="n">
-        <v>272</v>
+        <v>419.45</v>
       </c>
       <c r="F13" t="n">
-        <v>267.59</v>
+        <v>244.68</v>
       </c>
       <c r="G13" t="n">
-        <v>156.09</v>
+        <v>787.45</v>
       </c>
       <c r="H13" t="n">
-        <v>539.59</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
+        <v>247.45</v>
       </c>
     </row>
     <row r="14">
@@ -865,31 +800,26 @@
           <t>P03</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>P03｜平鎮3</t>
-        </is>
+      <c r="B14" t="n">
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D14" t="n">
-        <v>21</v>
+        <v>388</v>
       </c>
       <c r="E14" t="n">
-        <v>248</v>
+        <v>311.4</v>
       </c>
       <c r="F14" t="n">
-        <v>291</v>
+        <v>181.65</v>
       </c>
       <c r="G14" t="n">
-        <v>169.75</v>
+        <v>699.4</v>
       </c>
       <c r="H14" t="n">
-        <v>539</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
+        <v>159.4</v>
       </c>
     </row>
     <row r="15">
@@ -898,31 +828,26 @@
           <t>P03</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>P03｜平鎮3</t>
-        </is>
+      <c r="B15" t="n">
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>356</v>
       </c>
       <c r="E15" t="n">
-        <v>257</v>
+        <v>371.48</v>
       </c>
       <c r="F15" t="n">
-        <v>279.97</v>
+        <v>216.7</v>
       </c>
       <c r="G15" t="n">
-        <v>163.32</v>
+        <v>727.48</v>
       </c>
       <c r="H15" t="n">
-        <v>536.97</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
+        <v>187.48</v>
       </c>
     </row>
     <row r="16">
@@ -931,31 +856,26 @@
           <t>P03</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>P03｜平鎮3</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>411</v>
       </c>
       <c r="E16" t="n">
-        <v>280</v>
+        <v>354.36</v>
       </c>
       <c r="F16" t="n">
-        <v>259.74</v>
+        <v>206.71</v>
       </c>
       <c r="G16" t="n">
-        <v>151.52</v>
+        <v>765.36</v>
       </c>
       <c r="H16" t="n">
-        <v>539.74</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
+        <v>225.36</v>
       </c>
     </row>
     <row r="17">
@@ -964,31 +884,26 @@
           <t>P03</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>P03｜平鎮3</t>
-        </is>
+      <c r="B17" t="n">
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>341</v>
       </c>
       <c r="E17" t="n">
-        <v>272</v>
+        <v>371.93</v>
       </c>
       <c r="F17" t="n">
-        <v>267.36</v>
+        <v>216.96</v>
       </c>
       <c r="G17" t="n">
-        <v>155.96</v>
+        <v>712.9299999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>539.36</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
+        <v>172.93</v>
       </c>
     </row>
     <row r="18">
@@ -997,31 +912,26 @@
           <t>P03</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>P03｜平鎮3</t>
-        </is>
+      <c r="B18" t="n">
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
-        <v>23</v>
+        <v>384</v>
       </c>
       <c r="E18" t="n">
-        <v>272</v>
+        <v>358.56</v>
       </c>
       <c r="F18" t="n">
-        <v>249.31</v>
+        <v>209.16</v>
       </c>
       <c r="G18" t="n">
-        <v>145.43</v>
+        <v>742.5599999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>521.3099999999999</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
+        <v>202.56</v>
       </c>
     </row>
     <row r="19">
@@ -1030,31 +940,26 @@
           <t>P03</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>P03｜平鎮3</t>
-        </is>
+      <c r="B19" t="n">
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D19" t="n">
-        <v>21</v>
+        <v>432</v>
       </c>
       <c r="E19" t="n">
-        <v>248</v>
+        <v>326.22</v>
       </c>
       <c r="F19" t="n">
-        <v>289.68</v>
+        <v>190.29</v>
       </c>
       <c r="G19" t="n">
-        <v>168.98</v>
+        <v>758.22</v>
       </c>
       <c r="H19" t="n">
-        <v>537.6799999999999</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
+        <v>218.22</v>
       </c>
     </row>
     <row r="20">
@@ -1063,31 +968,26 @@
           <t>P04</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>P04｜平鎮4</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>456</v>
       </c>
       <c r="E20" t="n">
-        <v>256</v>
+        <v>428.57</v>
       </c>
       <c r="F20" t="n">
-        <v>280.5</v>
+        <v>250</v>
       </c>
       <c r="G20" t="n">
-        <v>163.63</v>
+        <v>884.5700000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>536.5</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
+        <v>344.57</v>
       </c>
     </row>
     <row r="21">
@@ -1096,31 +996,26 @@
           <t>P04</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>P04｜平鎮4</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D21" t="n">
-        <v>19</v>
+        <v>435</v>
       </c>
       <c r="E21" t="n">
-        <v>288</v>
+        <v>376.41</v>
       </c>
       <c r="F21" t="n">
-        <v>249.94</v>
+        <v>219.57</v>
       </c>
       <c r="G21" t="n">
-        <v>145.8</v>
+        <v>811.41</v>
       </c>
       <c r="H21" t="n">
-        <v>537.9400000000001</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
+        <v>271.41</v>
       </c>
     </row>
     <row r="22">
@@ -1129,31 +1024,26 @@
           <t>P04</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>P04｜平鎮4</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D22" t="n">
-        <v>22</v>
+        <v>322</v>
       </c>
       <c r="E22" t="n">
-        <v>318</v>
+        <v>354.15</v>
       </c>
       <c r="F22" t="n">
-        <v>218.42</v>
+        <v>206.58</v>
       </c>
       <c r="G22" t="n">
-        <v>127.41</v>
+        <v>676.15</v>
       </c>
       <c r="H22" t="n">
-        <v>536.42</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
+        <v>136.15</v>
       </c>
     </row>
     <row r="23">
@@ -1162,31 +1052,26 @@
           <t>P04</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>P04｜平鎮4</t>
-        </is>
+      <c r="B23" t="n">
+        <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D23" t="n">
-        <v>22</v>
+        <v>320</v>
       </c>
       <c r="E23" t="n">
-        <v>324</v>
+        <v>380.67</v>
       </c>
       <c r="F23" t="n">
-        <v>208.36</v>
+        <v>222.06</v>
       </c>
       <c r="G23" t="n">
-        <v>121.54</v>
+        <v>700.67</v>
       </c>
       <c r="H23" t="n">
-        <v>532.36</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
+        <v>160.67</v>
       </c>
     </row>
     <row r="24">
@@ -1195,31 +1080,26 @@
           <t>P04</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>P04｜平鎮4</t>
-        </is>
+      <c r="B24" t="n">
+        <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D24" t="n">
-        <v>22</v>
+        <v>423</v>
       </c>
       <c r="E24" t="n">
-        <v>272</v>
+        <v>391.04</v>
       </c>
       <c r="F24" t="n">
-        <v>261.77</v>
+        <v>228.11</v>
       </c>
       <c r="G24" t="n">
-        <v>152.7</v>
+        <v>814.04</v>
       </c>
       <c r="H24" t="n">
-        <v>533.77</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
+        <v>274.04</v>
       </c>
     </row>
     <row r="25">
@@ -1228,31 +1108,26 @@
           <t>P04</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>P04｜平鎮4</t>
-        </is>
+      <c r="B25" t="n">
+        <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="D25" t="n">
-        <v>26</v>
+        <v>370</v>
       </c>
       <c r="E25" t="n">
-        <v>317</v>
+        <v>427.59</v>
       </c>
       <c r="F25" t="n">
-        <v>222.94</v>
+        <v>249.43</v>
       </c>
       <c r="G25" t="n">
-        <v>130.05</v>
+        <v>797.59</v>
       </c>
       <c r="H25" t="n">
-        <v>539.9400000000001</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
+        <v>257.59</v>
       </c>
     </row>
     <row r="26">
@@ -1261,31 +1136,26 @@
           <t>P05</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>P05｜平鎮5</t>
-        </is>
+      <c r="B26" t="n">
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>22</v>
+        <v>288</v>
       </c>
       <c r="E26" t="n">
-        <v>260</v>
+        <v>388.88</v>
       </c>
       <c r="F26" t="n">
-        <v>277.05</v>
+        <v>226.85</v>
       </c>
       <c r="G26" t="n">
-        <v>161.61</v>
+        <v>676.88</v>
       </c>
       <c r="H26" t="n">
-        <v>537.05</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
+        <v>136.88</v>
       </c>
     </row>
     <row r="27">
@@ -1294,31 +1164,26 @@
           <t>P05</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>P05｜平鎮5</t>
-        </is>
+      <c r="B27" t="n">
+        <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D27" t="n">
-        <v>23</v>
+        <v>408</v>
       </c>
       <c r="E27" t="n">
-        <v>284</v>
+        <v>339.73</v>
       </c>
       <c r="F27" t="n">
-        <v>255.16</v>
+        <v>198.17</v>
       </c>
       <c r="G27" t="n">
-        <v>148.84</v>
+        <v>747.73</v>
       </c>
       <c r="H27" t="n">
-        <v>539.16</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
+        <v>207.73</v>
       </c>
     </row>
     <row r="28">
@@ -1327,31 +1192,26 @@
           <t>P05</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>P05｜平鎮5</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="D28" t="n">
-        <v>21</v>
+        <v>408</v>
       </c>
       <c r="E28" t="n">
-        <v>266</v>
+        <v>358.1</v>
       </c>
       <c r="F28" t="n">
-        <v>273.81</v>
+        <v>208.89</v>
       </c>
       <c r="G28" t="n">
-        <v>159.72</v>
+        <v>766.1</v>
       </c>
       <c r="H28" t="n">
-        <v>539.8099999999999</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
+        <v>226.1</v>
       </c>
     </row>
     <row r="29">
@@ -1360,31 +1220,26 @@
           <t>P05</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>P05｜平鎮5</t>
-        </is>
+      <c r="B29" t="n">
+        <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="D29" t="n">
-        <v>23</v>
+        <v>408</v>
       </c>
       <c r="E29" t="n">
-        <v>256</v>
+        <v>409.74</v>
       </c>
       <c r="F29" t="n">
-        <v>283.88</v>
+        <v>239.01</v>
       </c>
       <c r="G29" t="n">
-        <v>165.6</v>
+        <v>817.74</v>
       </c>
       <c r="H29" t="n">
-        <v>539.88</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
+        <v>277.74</v>
       </c>
     </row>
     <row r="30">
@@ -1393,31 +1248,26 @@
           <t>P05</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>P05｜平鎮5</t>
-        </is>
+      <c r="B30" t="n">
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="D30" t="n">
-        <v>23</v>
+        <v>408</v>
       </c>
       <c r="E30" t="n">
-        <v>272</v>
+        <v>438.47</v>
       </c>
       <c r="F30" t="n">
-        <v>266.48</v>
+        <v>255.77</v>
       </c>
       <c r="G30" t="n">
-        <v>155.45</v>
+        <v>846.47</v>
       </c>
       <c r="H30" t="n">
-        <v>538.48</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
+        <v>306.47</v>
       </c>
     </row>
     <row r="31">
@@ -1426,31 +1276,26 @@
           <t>P05</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>P05｜平鎮5</t>
-        </is>
+      <c r="B31" t="n">
+        <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D31" t="n">
-        <v>24</v>
+        <v>368</v>
       </c>
       <c r="E31" t="n">
-        <v>280</v>
+        <v>398.12</v>
       </c>
       <c r="F31" t="n">
-        <v>253.46</v>
+        <v>232.24</v>
       </c>
       <c r="G31" t="n">
-        <v>147.85</v>
+        <v>766.12</v>
       </c>
       <c r="H31" t="n">
-        <v>533.46</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
+        <v>226.12</v>
       </c>
     </row>
     <row r="32">
@@ -1459,31 +1304,26 @@
           <t>P06</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>P06｜平鎮6</t>
-        </is>
+      <c r="B32" t="n">
+        <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D32" t="n">
-        <v>22</v>
+        <v>392</v>
       </c>
       <c r="E32" t="n">
-        <v>264</v>
+        <v>413.96</v>
       </c>
       <c r="F32" t="n">
-        <v>275.2</v>
+        <v>241.48</v>
       </c>
       <c r="G32" t="n">
-        <v>160.53</v>
+        <v>805.96</v>
       </c>
       <c r="H32" t="n">
-        <v>539.2</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
+        <v>265.96</v>
       </c>
     </row>
     <row r="33">
@@ -1492,31 +1332,26 @@
           <t>P06</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>P06｜平鎮6</t>
-        </is>
+      <c r="B33" t="n">
+        <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D33" t="n">
-        <v>19</v>
+        <v>416</v>
       </c>
       <c r="E33" t="n">
-        <v>232</v>
+        <v>313.78</v>
       </c>
       <c r="F33" t="n">
-        <v>307.52</v>
+        <v>183.04</v>
       </c>
       <c r="G33" t="n">
-        <v>179.39</v>
+        <v>729.78</v>
       </c>
       <c r="H33" t="n">
-        <v>539.52</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
+        <v>189.78</v>
       </c>
     </row>
     <row r="34">
@@ -1525,31 +1360,26 @@
           <t>P06</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>P06｜平鎮6</t>
-        </is>
+      <c r="B34" t="n">
+        <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="D34" t="n">
-        <v>20</v>
+        <v>344</v>
       </c>
       <c r="E34" t="n">
-        <v>264</v>
+        <v>477.84</v>
       </c>
       <c r="F34" t="n">
-        <v>271.4</v>
+        <v>278.74</v>
       </c>
       <c r="G34" t="n">
-        <v>158.31</v>
+        <v>821.84</v>
       </c>
       <c r="H34" t="n">
-        <v>535.4</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
+        <v>281.84</v>
       </c>
     </row>
     <row r="35">
@@ -1558,31 +1388,26 @@
           <t>P06</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>P06｜平鎮6</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="D35" t="n">
-        <v>24</v>
+        <v>376</v>
       </c>
       <c r="E35" t="n">
-        <v>278</v>
+        <v>372.98</v>
       </c>
       <c r="F35" t="n">
-        <v>259.55</v>
+        <v>217.57</v>
       </c>
       <c r="G35" t="n">
-        <v>151.41</v>
+        <v>748.98</v>
       </c>
       <c r="H35" t="n">
-        <v>537.55</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
+        <v>208.98</v>
       </c>
     </row>
     <row r="36">
@@ -1591,31 +1416,26 @@
           <t>P06</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>P06｜平鎮6</t>
-        </is>
+      <c r="B36" t="n">
+        <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="D36" t="n">
-        <v>19</v>
+        <v>376</v>
       </c>
       <c r="E36" t="n">
-        <v>240</v>
+        <v>405.72</v>
       </c>
       <c r="F36" t="n">
-        <v>298.32</v>
+        <v>236.67</v>
       </c>
       <c r="G36" t="n">
-        <v>174.02</v>
+        <v>781.72</v>
       </c>
       <c r="H36" t="n">
-        <v>538.3200000000001</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
+        <v>241.72</v>
       </c>
     </row>
     <row r="37">
@@ -1624,31 +1444,26 @@
           <t>P06</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>P06｜平鎮6</t>
-        </is>
+      <c r="B37" t="n">
+        <v>6</v>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D37" t="n">
-        <v>24</v>
+        <v>368</v>
       </c>
       <c r="E37" t="n">
-        <v>268</v>
+        <v>377.06</v>
       </c>
       <c r="F37" t="n">
-        <v>268.43</v>
+        <v>219.95</v>
       </c>
       <c r="G37" t="n">
-        <v>156.59</v>
+        <v>745.0599999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>536.4299999999999</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
+        <v>205.06</v>
       </c>
     </row>
     <row r="38">
@@ -1657,31 +1472,26 @@
           <t>P07</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>P07｜平鎮7</t>
-        </is>
+      <c r="B38" t="n">
+        <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D38" t="n">
-        <v>26</v>
+        <v>357</v>
       </c>
       <c r="E38" t="n">
-        <v>272</v>
+        <v>424.87</v>
       </c>
       <c r="F38" t="n">
-        <v>265.41</v>
+        <v>247.84</v>
       </c>
       <c r="G38" t="n">
-        <v>154.82</v>
+        <v>781.87</v>
       </c>
       <c r="H38" t="n">
-        <v>537.41</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
+        <v>241.87</v>
       </c>
     </row>
     <row r="39">
@@ -1690,31 +1500,26 @@
           <t>P07</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>P07｜平鎮7</t>
-        </is>
+      <c r="B39" t="n">
+        <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D39" t="n">
-        <v>23</v>
+        <v>346</v>
       </c>
       <c r="E39" t="n">
-        <v>273</v>
+        <v>291.52</v>
       </c>
       <c r="F39" t="n">
-        <v>264.3</v>
+        <v>170.05</v>
       </c>
       <c r="G39" t="n">
-        <v>154.17</v>
+        <v>637.52</v>
       </c>
       <c r="H39" t="n">
-        <v>537.3</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
+        <v>97.52</v>
       </c>
     </row>
     <row r="40">
@@ -1723,31 +1528,26 @@
           <t>P07</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>P07｜平鎮7</t>
-        </is>
+      <c r="B40" t="n">
+        <v>3</v>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D40" t="n">
-        <v>23</v>
+        <v>289</v>
       </c>
       <c r="E40" t="n">
-        <v>263</v>
+        <v>355.34</v>
       </c>
       <c r="F40" t="n">
-        <v>276.85</v>
+        <v>207.28</v>
       </c>
       <c r="G40" t="n">
-        <v>161.5</v>
+        <v>644.34</v>
       </c>
       <c r="H40" t="n">
-        <v>539.85</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
+        <v>104.34</v>
       </c>
     </row>
     <row r="41">
@@ -1756,31 +1556,26 @@
           <t>P07</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>P07｜平鎮7</t>
-        </is>
+      <c r="B41" t="n">
+        <v>4</v>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="D41" t="n">
-        <v>24</v>
+        <v>336</v>
       </c>
       <c r="E41" t="n">
-        <v>303</v>
+        <v>477.46</v>
       </c>
       <c r="F41" t="n">
-        <v>236.96</v>
+        <v>278.52</v>
       </c>
       <c r="G41" t="n">
-        <v>138.22</v>
+        <v>813.46</v>
       </c>
       <c r="H41" t="n">
-        <v>539.96</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
+        <v>273.46</v>
       </c>
     </row>
     <row r="42">
@@ -1789,31 +1584,26 @@
           <t>P07</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>P07｜平鎮7</t>
-        </is>
+      <c r="B42" t="n">
+        <v>5</v>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="D42" t="n">
-        <v>22</v>
+        <v>312</v>
       </c>
       <c r="E42" t="n">
-        <v>240</v>
+        <v>451.59</v>
       </c>
       <c r="F42" t="n">
-        <v>298.48</v>
+        <v>263.42</v>
       </c>
       <c r="G42" t="n">
-        <v>174.11</v>
+        <v>763.59</v>
       </c>
       <c r="H42" t="n">
-        <v>538.48</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
+        <v>223.59</v>
       </c>
     </row>
     <row r="43">
@@ -1822,31 +1612,26 @@
           <t>P07</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>P07｜平鎮7</t>
-        </is>
+      <c r="B43" t="n">
+        <v>6</v>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="D43" t="n">
-        <v>23</v>
+        <v>354</v>
       </c>
       <c r="E43" t="n">
-        <v>264</v>
+        <v>481.58</v>
       </c>
       <c r="F43" t="n">
-        <v>271.08</v>
+        <v>280.92</v>
       </c>
       <c r="G43" t="n">
-        <v>158.13</v>
+        <v>835.58</v>
       </c>
       <c r="H43" t="n">
-        <v>535.08</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
+        <v>295.58</v>
       </c>
     </row>
     <row r="44">
@@ -1855,31 +1640,26 @@
           <t>P08</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>P08｜平鎮8</t>
-        </is>
+      <c r="B44" t="n">
+        <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D44" t="n">
-        <v>22</v>
+        <v>277</v>
       </c>
       <c r="E44" t="n">
-        <v>232</v>
+        <v>422.12</v>
       </c>
       <c r="F44" t="n">
-        <v>305.68</v>
+        <v>246.24</v>
       </c>
       <c r="G44" t="n">
-        <v>178.32</v>
+        <v>699.12</v>
       </c>
       <c r="H44" t="n">
-        <v>537.6799999999999</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
+        <v>159.12</v>
       </c>
     </row>
     <row r="45">
@@ -1888,31 +1668,26 @@
           <t>P08</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>P08｜平鎮8</t>
-        </is>
+      <c r="B45" t="n">
+        <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D45" t="n">
-        <v>25</v>
+        <v>324</v>
       </c>
       <c r="E45" t="n">
-        <v>306</v>
+        <v>438.8</v>
       </c>
       <c r="F45" t="n">
-        <v>229.52</v>
+        <v>255.97</v>
       </c>
       <c r="G45" t="n">
-        <v>133.88</v>
+        <v>762.8</v>
       </c>
       <c r="H45" t="n">
-        <v>535.52</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
+        <v>222.8</v>
       </c>
     </row>
     <row r="46">
@@ -1921,31 +1696,26 @@
           <t>P08</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>P08｜平鎮8</t>
-        </is>
+      <c r="B46" t="n">
+        <v>3</v>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="D46" t="n">
-        <v>26</v>
+        <v>356</v>
       </c>
       <c r="E46" t="n">
-        <v>264</v>
+        <v>412.8</v>
       </c>
       <c r="F46" t="n">
-        <v>271.41</v>
+        <v>240.8</v>
       </c>
       <c r="G46" t="n">
-        <v>158.32</v>
+        <v>768.8</v>
       </c>
       <c r="H46" t="n">
-        <v>535.41</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
+        <v>228.8</v>
       </c>
     </row>
     <row r="47">
@@ -1954,31 +1724,26 @@
           <t>P08</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>P08｜平鎮8</t>
-        </is>
+      <c r="B47" t="n">
+        <v>4</v>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D47" t="n">
-        <v>24</v>
+        <v>320</v>
       </c>
       <c r="E47" t="n">
-        <v>272</v>
+        <v>375.63</v>
       </c>
       <c r="F47" t="n">
-        <v>262.47</v>
+        <v>219.12</v>
       </c>
       <c r="G47" t="n">
-        <v>153.11</v>
+        <v>695.63</v>
       </c>
       <c r="H47" t="n">
-        <v>534.47</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
+        <v>155.63</v>
       </c>
     </row>
     <row r="48">
@@ -1987,31 +1752,26 @@
           <t>P08</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>P08｜平鎮8</t>
-        </is>
+      <c r="B48" t="n">
+        <v>5</v>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D48" t="n">
-        <v>24</v>
+        <v>344</v>
       </c>
       <c r="E48" t="n">
-        <v>256</v>
+        <v>424.56</v>
       </c>
       <c r="F48" t="n">
-        <v>283.02</v>
+        <v>247.66</v>
       </c>
       <c r="G48" t="n">
-        <v>165.09</v>
+        <v>768.5599999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>539.02</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
+        <v>228.56</v>
       </c>
     </row>
     <row r="49">
@@ -2020,31 +1780,26 @@
           <t>P08</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>P08｜平鎮8</t>
-        </is>
+      <c r="B49" t="n">
+        <v>6</v>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D49" t="n">
-        <v>24</v>
+        <v>368</v>
       </c>
       <c r="E49" t="n">
-        <v>264</v>
+        <v>397.76</v>
       </c>
       <c r="F49" t="n">
-        <v>274.15</v>
+        <v>232.02</v>
       </c>
       <c r="G49" t="n">
-        <v>159.92</v>
+        <v>765.76</v>
       </c>
       <c r="H49" t="n">
-        <v>538.15</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
+        <v>225.76</v>
       </c>
     </row>
     <row r="50">
@@ -2053,31 +1808,26 @@
           <t>P09</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>P09｜平鎮9</t>
-        </is>
+      <c r="B50" t="n">
+        <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D50" t="n">
-        <v>23</v>
+        <v>339</v>
       </c>
       <c r="E50" t="n">
-        <v>256</v>
+        <v>415.12</v>
       </c>
       <c r="F50" t="n">
-        <v>283.82</v>
+        <v>242.15</v>
       </c>
       <c r="G50" t="n">
-        <v>165.56</v>
+        <v>754.12</v>
       </c>
       <c r="H50" t="n">
-        <v>539.8200000000001</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
+        <v>214.12</v>
       </c>
     </row>
     <row r="51">
@@ -2086,31 +1836,26 @@
           <t>P09</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>P09｜平鎮9</t>
-        </is>
+      <c r="B51" t="n">
+        <v>2</v>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D51" t="n">
-        <v>23</v>
+        <v>314.5</v>
       </c>
       <c r="E51" t="n">
-        <v>254</v>
+        <v>368.64</v>
       </c>
       <c r="F51" t="n">
-        <v>285.88</v>
+        <v>215.04</v>
       </c>
       <c r="G51" t="n">
-        <v>166.76</v>
+        <v>683.14</v>
       </c>
       <c r="H51" t="n">
-        <v>539.88</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
+        <v>143.14</v>
       </c>
     </row>
     <row r="52">
@@ -2119,31 +1864,26 @@
           <t>P09</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>P09｜平鎮9</t>
-        </is>
+      <c r="B52" t="n">
+        <v>3</v>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="D52" t="n">
-        <v>19</v>
+        <v>362</v>
       </c>
       <c r="E52" t="n">
-        <v>224</v>
+        <v>453.19</v>
       </c>
       <c r="F52" t="n">
-        <v>315.99</v>
+        <v>264.36</v>
       </c>
       <c r="G52" t="n">
-        <v>184.33</v>
+        <v>815.1900000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>539.99</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
+        <v>275.19</v>
       </c>
     </row>
     <row r="53">
@@ -2152,31 +1892,26 @@
           <t>P09</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>P09｜平鎮9</t>
-        </is>
+      <c r="B53" t="n">
+        <v>4</v>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D53" t="n">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="E53" t="n">
-        <v>264</v>
+        <v>432.29</v>
       </c>
       <c r="F53" t="n">
-        <v>273.81</v>
+        <v>252.17</v>
       </c>
       <c r="G53" t="n">
-        <v>159.72</v>
+        <v>664.29</v>
       </c>
       <c r="H53" t="n">
-        <v>537.8099999999999</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
+        <v>124.29</v>
       </c>
     </row>
     <row r="54">
@@ -2185,31 +1920,26 @@
           <t>P09</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>P09｜平鎮9</t>
-        </is>
+      <c r="B54" t="n">
+        <v>5</v>
       </c>
       <c r="C54" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="D54" t="n">
-        <v>22</v>
+        <v>320</v>
       </c>
       <c r="E54" t="n">
-        <v>300</v>
+        <v>369.54</v>
       </c>
       <c r="F54" t="n">
-        <v>237.49</v>
+        <v>215.56</v>
       </c>
       <c r="G54" t="n">
-        <v>138.54</v>
+        <v>689.54</v>
       </c>
       <c r="H54" t="n">
-        <v>537.49</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
+        <v>149.54</v>
       </c>
     </row>
     <row r="55">
@@ -2218,31 +1948,26 @@
           <t>P09</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>P09｜平鎮9</t>
-        </is>
+      <c r="B55" t="n">
+        <v>6</v>
       </c>
       <c r="C55" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="D55" t="n">
-        <v>24</v>
+        <v>376</v>
       </c>
       <c r="E55" t="n">
-        <v>264</v>
+        <v>331.33</v>
       </c>
       <c r="F55" t="n">
-        <v>259.98</v>
+        <v>193.28</v>
       </c>
       <c r="G55" t="n">
-        <v>151.66</v>
+        <v>707.33</v>
       </c>
       <c r="H55" t="n">
-        <v>523.98</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
+        <v>167.33</v>
       </c>
     </row>
     <row r="56">
@@ -2251,31 +1976,26 @@
           <t>P10</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>P10｜平鎮10</t>
-        </is>
+      <c r="B56" t="n">
+        <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D56" t="n">
-        <v>25</v>
+        <v>248</v>
       </c>
       <c r="E56" t="n">
-        <v>296</v>
+        <v>505.71</v>
       </c>
       <c r="F56" t="n">
-        <v>242.69</v>
+        <v>295</v>
       </c>
       <c r="G56" t="n">
-        <v>141.57</v>
+        <v>753.71</v>
       </c>
       <c r="H56" t="n">
-        <v>538.6900000000001</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
+        <v>213.71</v>
       </c>
     </row>
     <row r="57">
@@ -2284,31 +2004,26 @@
           <t>P10</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>P10｜平鎮10</t>
-        </is>
+      <c r="B57" t="n">
+        <v>2</v>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D57" t="n">
-        <v>25</v>
+        <v>264</v>
       </c>
       <c r="E57" t="n">
-        <v>303</v>
+        <v>530.42</v>
       </c>
       <c r="F57" t="n">
-        <v>236.72</v>
+        <v>309.41</v>
       </c>
       <c r="G57" t="n">
-        <v>138.09</v>
+        <v>794.42</v>
       </c>
       <c r="H57" t="n">
-        <v>539.72</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
+        <v>254.42</v>
       </c>
     </row>
     <row r="58">
@@ -2317,31 +2032,26 @@
           <t>P10</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>P10｜平鎮10</t>
-        </is>
+      <c r="B58" t="n">
+        <v>3</v>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="D58" t="n">
-        <v>23</v>
+        <v>352</v>
       </c>
       <c r="E58" t="n">
-        <v>261</v>
+        <v>321.67</v>
       </c>
       <c r="F58" t="n">
-        <v>272.76</v>
+        <v>187.64</v>
       </c>
       <c r="G58" t="n">
-        <v>159.11</v>
+        <v>673.67</v>
       </c>
       <c r="H58" t="n">
-        <v>533.76</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
+        <v>133.67</v>
       </c>
     </row>
     <row r="59">
@@ -2350,31 +2060,26 @@
           <t>P10</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>P10｜平鎮10</t>
-        </is>
+      <c r="B59" t="n">
+        <v>4</v>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="D59" t="n">
-        <v>23</v>
+        <v>320</v>
       </c>
       <c r="E59" t="n">
-        <v>272</v>
+        <v>334.33</v>
       </c>
       <c r="F59" t="n">
-        <v>267.53</v>
+        <v>195.03</v>
       </c>
       <c r="G59" t="n">
-        <v>156.06</v>
+        <v>654.33</v>
       </c>
       <c r="H59" t="n">
-        <v>539.53</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0</v>
+        <v>114.33</v>
       </c>
     </row>
     <row r="60">
@@ -2383,31 +2088,26 @@
           <t>P10</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>P10｜平鎮10</t>
-        </is>
+      <c r="B60" t="n">
+        <v>5</v>
       </c>
       <c r="C60" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="D60" t="n">
-        <v>21</v>
+        <v>299</v>
       </c>
       <c r="E60" t="n">
-        <v>271</v>
+        <v>547.84</v>
       </c>
       <c r="F60" t="n">
-        <v>268.6</v>
+        <v>319.57</v>
       </c>
       <c r="G60" t="n">
-        <v>156.68</v>
+        <v>846.84</v>
       </c>
       <c r="H60" t="n">
-        <v>539.6</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
+        <v>306.84</v>
       </c>
     </row>
     <row r="61">
@@ -2416,31 +2116,26 @@
           <t>P10</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>P10｜平鎮10</t>
-        </is>
+      <c r="B61" t="n">
+        <v>6</v>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="D61" t="n">
-        <v>23</v>
+        <v>312</v>
       </c>
       <c r="E61" t="n">
-        <v>288</v>
+        <v>345.62</v>
       </c>
       <c r="F61" t="n">
-        <v>250.12</v>
+        <v>201.61</v>
       </c>
       <c r="G61" t="n">
-        <v>145.9</v>
+        <v>657.62</v>
       </c>
       <c r="H61" t="n">
-        <v>538.12</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0</v>
+        <v>117.62</v>
       </c>
     </row>
     <row r="62">
@@ -2449,31 +2144,26 @@
           <t>P11</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>P11｜平鎮11</t>
-        </is>
+      <c r="B62" t="n">
+        <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D62" t="n">
-        <v>23</v>
+        <v>176</v>
       </c>
       <c r="E62" t="n">
-        <v>256</v>
+        <v>513.08</v>
       </c>
       <c r="F62" t="n">
-        <v>275.19</v>
+        <v>299.3</v>
       </c>
       <c r="G62" t="n">
-        <v>160.53</v>
+        <v>689.08</v>
       </c>
       <c r="H62" t="n">
-        <v>531.1900000000001</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
+        <v>149.08</v>
       </c>
     </row>
     <row r="63">
@@ -2482,31 +2172,26 @@
           <t>P11</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>P11｜平鎮11</t>
-        </is>
+      <c r="B63" t="n">
+        <v>2</v>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D63" t="n">
-        <v>24</v>
+        <v>355</v>
       </c>
       <c r="E63" t="n">
-        <v>312</v>
+        <v>327.32</v>
       </c>
       <c r="F63" t="n">
-        <v>212.87</v>
+        <v>190.94</v>
       </c>
       <c r="G63" t="n">
-        <v>124.18</v>
+        <v>682.3200000000001</v>
       </c>
       <c r="H63" t="n">
-        <v>524.87</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
+        <v>142.32</v>
       </c>
     </row>
     <row r="64">
@@ -2515,31 +2200,26 @@
           <t>P11</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>P11｜平鎮11</t>
-        </is>
+      <c r="B64" t="n">
+        <v>3</v>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D64" t="n">
-        <v>19</v>
+        <v>296</v>
       </c>
       <c r="E64" t="n">
-        <v>304</v>
+        <v>393.64</v>
       </c>
       <c r="F64" t="n">
-        <v>235.53</v>
+        <v>229.62</v>
       </c>
       <c r="G64" t="n">
-        <v>137.39</v>
+        <v>689.64</v>
       </c>
       <c r="H64" t="n">
-        <v>539.53</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0</v>
+        <v>149.64</v>
       </c>
     </row>
     <row r="65">
@@ -2548,31 +2228,26 @@
           <t>P11</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>P11｜平鎮11</t>
-        </is>
+      <c r="B65" t="n">
+        <v>4</v>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D65" t="n">
-        <v>20</v>
+        <v>272</v>
       </c>
       <c r="E65" t="n">
-        <v>224</v>
+        <v>427.74</v>
       </c>
       <c r="F65" t="n">
-        <v>314.26</v>
+        <v>249.52</v>
       </c>
       <c r="G65" t="n">
-        <v>183.32</v>
+        <v>699.74</v>
       </c>
       <c r="H65" t="n">
-        <v>538.26</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0</v>
+        <v>159.74</v>
       </c>
     </row>
     <row r="66">
@@ -2581,31 +2256,26 @@
           <t>P11</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>P11｜平鎮11</t>
-        </is>
+      <c r="B66" t="n">
+        <v>5</v>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D66" t="n">
-        <v>20</v>
+        <v>368</v>
       </c>
       <c r="E66" t="n">
-        <v>248</v>
+        <v>367.94</v>
       </c>
       <c r="F66" t="n">
-        <v>291.96</v>
+        <v>214.63</v>
       </c>
       <c r="G66" t="n">
-        <v>170.31</v>
+        <v>735.9400000000001</v>
       </c>
       <c r="H66" t="n">
-        <v>539.96</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
+        <v>195.94</v>
       </c>
     </row>
     <row r="67">
@@ -2614,31 +2284,26 @@
           <t>P11</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>P11｜平鎮11</t>
-        </is>
+      <c r="B67" t="n">
+        <v>6</v>
       </c>
       <c r="C67" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D67" t="n">
-        <v>23</v>
+        <v>336</v>
       </c>
       <c r="E67" t="n">
-        <v>283</v>
+        <v>322.63</v>
       </c>
       <c r="F67" t="n">
-        <v>254.36</v>
+        <v>188.2</v>
       </c>
       <c r="G67" t="n">
-        <v>148.37</v>
+        <v>658.63</v>
       </c>
       <c r="H67" t="n">
-        <v>537.36</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0</v>
+        <v>118.63</v>
       </c>
     </row>
     <row r="68">
@@ -2647,31 +2312,26 @@
           <t>P12</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>P12｜平鎮12</t>
-        </is>
+      <c r="B68" t="n">
+        <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D68" t="n">
-        <v>24</v>
+        <v>280</v>
       </c>
       <c r="E68" t="n">
-        <v>264</v>
+        <v>423.22</v>
       </c>
       <c r="F68" t="n">
-        <v>275.38</v>
+        <v>246.88</v>
       </c>
       <c r="G68" t="n">
-        <v>160.64</v>
+        <v>703.22</v>
       </c>
       <c r="H68" t="n">
-        <v>539.38</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0</v>
+        <v>163.22</v>
       </c>
     </row>
     <row r="69">
@@ -2680,31 +2340,26 @@
           <t>P12</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>P12｜平鎮12</t>
-        </is>
+      <c r="B69" t="n">
+        <v>2</v>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="D69" t="n">
-        <v>25</v>
+        <v>360</v>
       </c>
       <c r="E69" t="n">
-        <v>303</v>
+        <v>301.17</v>
       </c>
       <c r="F69" t="n">
-        <v>236.53</v>
+        <v>175.69</v>
       </c>
       <c r="G69" t="n">
-        <v>137.98</v>
+        <v>661.17</v>
       </c>
       <c r="H69" t="n">
-        <v>539.53</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0</v>
+        <v>121.17</v>
       </c>
     </row>
     <row r="70">
@@ -2713,31 +2368,26 @@
           <t>P12</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>P12｜平鎮12</t>
-        </is>
+      <c r="B70" t="n">
+        <v>3</v>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="D70" t="n">
-        <v>19</v>
+        <v>304</v>
       </c>
       <c r="E70" t="n">
-        <v>256</v>
+        <v>440.36</v>
       </c>
       <c r="F70" t="n">
-        <v>279.36</v>
+        <v>256.87</v>
       </c>
       <c r="G70" t="n">
-        <v>162.96</v>
+        <v>744.36</v>
       </c>
       <c r="H70" t="n">
-        <v>535.36</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
+        <v>204.36</v>
       </c>
     </row>
     <row r="71">
@@ -2746,31 +2396,26 @@
           <t>P12</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>P12｜平鎮12</t>
-        </is>
+      <c r="B71" t="n">
+        <v>4</v>
       </c>
       <c r="C71" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="D71" t="n">
-        <v>21</v>
+        <v>312</v>
       </c>
       <c r="E71" t="n">
-        <v>236</v>
+        <v>404.86</v>
       </c>
       <c r="F71" t="n">
-        <v>301.55</v>
+        <v>236.17</v>
       </c>
       <c r="G71" t="n">
-        <v>175.9</v>
+        <v>716.86</v>
       </c>
       <c r="H71" t="n">
-        <v>537.55</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
+        <v>176.86</v>
       </c>
     </row>
     <row r="72">
@@ -2779,31 +2424,26 @@
           <t>P12</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>P12｜平鎮12</t>
-        </is>
+      <c r="B72" t="n">
+        <v>5</v>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D72" t="n">
-        <v>25</v>
+        <v>263</v>
       </c>
       <c r="E72" t="n">
-        <v>266</v>
+        <v>495.53</v>
       </c>
       <c r="F72" t="n">
-        <v>273.82</v>
+        <v>289.06</v>
       </c>
       <c r="G72" t="n">
-        <v>159.73</v>
+        <v>758.53</v>
       </c>
       <c r="H72" t="n">
-        <v>539.8200000000001</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
+        <v>218.53</v>
       </c>
     </row>
     <row r="73">
@@ -2812,31 +2452,26 @@
           <t>P12</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>P12｜平鎮12</t>
-        </is>
+      <c r="B73" t="n">
+        <v>6</v>
       </c>
       <c r="C73" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D73" t="n">
-        <v>23</v>
+        <v>280</v>
       </c>
       <c r="E73" t="n">
-        <v>258</v>
+        <v>383.69</v>
       </c>
       <c r="F73" t="n">
-        <v>280.67</v>
+        <v>223.82</v>
       </c>
       <c r="G73" t="n">
-        <v>163.73</v>
+        <v>663.6900000000001</v>
       </c>
       <c r="H73" t="n">
-        <v>538.67</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
+        <v>123.69</v>
       </c>
     </row>
     <row r="74">
@@ -2845,30 +2480,25 @@
           <t>W01</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>W01｜五股1</t>
-        </is>
+      <c r="B74" t="n">
+        <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D74" t="n">
-        <v>16</v>
+        <v>312</v>
       </c>
       <c r="E74" t="n">
-        <v>304</v>
+        <v>123.77</v>
       </c>
       <c r="F74" t="n">
-        <v>103.64</v>
+        <v>72.2</v>
       </c>
       <c r="G74" t="n">
-        <v>60.46</v>
+        <v>435.77</v>
       </c>
       <c r="H74" t="n">
-        <v>407.64</v>
-      </c>
-      <c r="I74" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2878,30 +2508,25 @@
           <t>W01</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>W01｜五股1</t>
-        </is>
+      <c r="B75" t="n">
+        <v>2</v>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D75" t="n">
-        <v>20</v>
+        <v>216</v>
       </c>
       <c r="E75" t="n">
-        <v>286</v>
+        <v>207.02</v>
       </c>
       <c r="F75" t="n">
-        <v>119.75</v>
+        <v>120.76</v>
       </c>
       <c r="G75" t="n">
-        <v>69.84999999999999</v>
+        <v>423.02</v>
       </c>
       <c r="H75" t="n">
-        <v>405.75</v>
-      </c>
-      <c r="I75" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2911,30 +2536,25 @@
           <t>W01</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>W01｜五股1</t>
-        </is>
+      <c r="B76" t="n">
+        <v>3</v>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D76" t="n">
-        <v>17</v>
+        <v>248</v>
       </c>
       <c r="E76" t="n">
-        <v>224</v>
+        <v>201.41</v>
       </c>
       <c r="F76" t="n">
-        <v>171.24</v>
+        <v>117.49</v>
       </c>
       <c r="G76" t="n">
-        <v>99.89</v>
+        <v>449.41</v>
       </c>
       <c r="H76" t="n">
-        <v>395.24</v>
-      </c>
-      <c r="I76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2944,30 +2564,25 @@
           <t>W01</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>W01｜五股1</t>
-        </is>
+      <c r="B77" t="n">
+        <v>4</v>
       </c>
       <c r="C77" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D77" t="n">
-        <v>15</v>
+        <v>221</v>
       </c>
       <c r="E77" t="n">
-        <v>176</v>
+        <v>195.74</v>
       </c>
       <c r="F77" t="n">
-        <v>234.75</v>
+        <v>114.18</v>
       </c>
       <c r="G77" t="n">
-        <v>136.94</v>
+        <v>416.74</v>
       </c>
       <c r="H77" t="n">
-        <v>410.75</v>
-      </c>
-      <c r="I77" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2977,30 +2592,25 @@
           <t>W01</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>W01｜五股1</t>
-        </is>
+      <c r="B78" t="n">
+        <v>5</v>
       </c>
       <c r="C78" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D78" t="n">
-        <v>17</v>
+        <v>200</v>
       </c>
       <c r="E78" t="n">
-        <v>200</v>
+        <v>157.84</v>
       </c>
       <c r="F78" t="n">
-        <v>204.13</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>119.08</v>
+        <v>357.84</v>
       </c>
       <c r="H78" t="n">
-        <v>404.13</v>
-      </c>
-      <c r="I78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3010,30 +2620,25 @@
           <t>W01</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>W01｜五股1</t>
-        </is>
+      <c r="B79" t="n">
+        <v>6</v>
       </c>
       <c r="C79" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D79" t="n">
-        <v>18</v>
+        <v>219</v>
       </c>
       <c r="E79" t="n">
-        <v>208</v>
+        <v>212.08</v>
       </c>
       <c r="F79" t="n">
-        <v>190.27</v>
+        <v>123.71</v>
       </c>
       <c r="G79" t="n">
-        <v>110.99</v>
+        <v>431.08</v>
       </c>
       <c r="H79" t="n">
-        <v>398.27</v>
-      </c>
-      <c r="I79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3043,30 +2648,25 @@
           <t>W02</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>W02｜五股2</t>
-        </is>
+      <c r="B80" t="n">
+        <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D80" t="n">
-        <v>17</v>
+        <v>216</v>
       </c>
       <c r="E80" t="n">
-        <v>200</v>
+        <v>188.55</v>
       </c>
       <c r="F80" t="n">
-        <v>202.09</v>
+        <v>109.99</v>
       </c>
       <c r="G80" t="n">
-        <v>117.89</v>
+        <v>404.55</v>
       </c>
       <c r="H80" t="n">
-        <v>402.09</v>
-      </c>
-      <c r="I80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3076,30 +2676,25 @@
           <t>W02</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>W02｜五股2</t>
-        </is>
+      <c r="B81" t="n">
+        <v>2</v>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D81" t="n">
-        <v>17</v>
+        <v>208</v>
       </c>
       <c r="E81" t="n">
-        <v>208</v>
+        <v>153.83</v>
       </c>
       <c r="F81" t="n">
-        <v>193.02</v>
+        <v>89.73</v>
       </c>
       <c r="G81" t="n">
-        <v>112.59</v>
+        <v>361.83</v>
       </c>
       <c r="H81" t="n">
-        <v>401.02</v>
-      </c>
-      <c r="I81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3109,30 +2704,25 @@
           <t>W02</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>W02｜五股2</t>
-        </is>
+      <c r="B82" t="n">
+        <v>3</v>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D82" t="n">
-        <v>17</v>
+        <v>216</v>
       </c>
       <c r="E82" t="n">
-        <v>207</v>
+        <v>160.36</v>
       </c>
       <c r="F82" t="n">
-        <v>196.19</v>
+        <v>93.55</v>
       </c>
       <c r="G82" t="n">
-        <v>114.44</v>
+        <v>376.36</v>
       </c>
       <c r="H82" t="n">
-        <v>403.19</v>
-      </c>
-      <c r="I82" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3142,30 +2732,25 @@
           <t>W02</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>W02｜五股2</t>
-        </is>
+      <c r="B83" t="n">
+        <v>4</v>
       </c>
       <c r="C83" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D83" t="n">
-        <v>17</v>
+        <v>190</v>
       </c>
       <c r="E83" t="n">
-        <v>209</v>
+        <v>199.42</v>
       </c>
       <c r="F83" t="n">
-        <v>193.64</v>
+        <v>116.33</v>
       </c>
       <c r="G83" t="n">
-        <v>112.96</v>
+        <v>389.42</v>
       </c>
       <c r="H83" t="n">
-        <v>402.64</v>
-      </c>
-      <c r="I83" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3175,30 +2760,25 @@
           <t>W02</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>W02｜五股2</t>
-        </is>
+      <c r="B84" t="n">
+        <v>5</v>
       </c>
       <c r="C84" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D84" t="n">
-        <v>17</v>
+        <v>192</v>
       </c>
       <c r="E84" t="n">
-        <v>192</v>
+        <v>198.01</v>
       </c>
       <c r="F84" t="n">
-        <v>215.2</v>
+        <v>115.5</v>
       </c>
       <c r="G84" t="n">
-        <v>125.53</v>
+        <v>390.01</v>
       </c>
       <c r="H84" t="n">
-        <v>407.2</v>
-      </c>
-      <c r="I84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3208,30 +2788,25 @@
           <t>W02</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>W02｜五股2</t>
-        </is>
+      <c r="B85" t="n">
+        <v>6</v>
       </c>
       <c r="C85" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D85" t="n">
-        <v>18</v>
+        <v>184</v>
       </c>
       <c r="E85" t="n">
-        <v>208</v>
+        <v>219.6</v>
       </c>
       <c r="F85" t="n">
-        <v>179.83</v>
+        <v>128.1</v>
       </c>
       <c r="G85" t="n">
-        <v>104.9</v>
+        <v>403.6</v>
       </c>
       <c r="H85" t="n">
-        <v>387.83</v>
-      </c>
-      <c r="I85" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/Daily_Route_Summary_compact.xlsx
+++ b/output/Daily_Route_Summary_compact.xlsx
@@ -2092,22 +2092,22 @@
         <v>5</v>
       </c>
       <c r="C60" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D60" t="n">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E60" t="n">
-        <v>547.84</v>
+        <v>393.11</v>
       </c>
       <c r="F60" t="n">
-        <v>319.57</v>
+        <v>229.31</v>
       </c>
       <c r="G60" t="n">
-        <v>846.84</v>
+        <v>689.11</v>
       </c>
       <c r="H60" t="n">
-        <v>306.84</v>
+        <v>149.11</v>
       </c>
     </row>
     <row r="61">
@@ -2176,22 +2176,22 @@
         <v>2</v>
       </c>
       <c r="C63" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D63" t="n">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="E63" t="n">
-        <v>327.32</v>
+        <v>324.91</v>
       </c>
       <c r="F63" t="n">
-        <v>190.94</v>
+        <v>189.53</v>
       </c>
       <c r="G63" t="n">
-        <v>682.3200000000001</v>
+        <v>676.91</v>
       </c>
       <c r="H63" t="n">
-        <v>142.32</v>
+        <v>136.91</v>
       </c>
     </row>
     <row r="64">

--- a/output/Daily_Route_Summary_compact.xlsx
+++ b/output/Daily_Route_Summary_compact.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,46 +425,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>driver</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>driver_label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>schedule_slot</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>day</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>stop_count</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>service_min</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>drive_min</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>dist_km</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>total_min</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>overtime_min</t>
         </is>
@@ -464,26 +486,36 @@
           <t>P01</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P01｜平鎮1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
-        <v>27</v>
-      </c>
-      <c r="D2" t="n">
-        <v>473</v>
-      </c>
       <c r="E2" t="n">
-        <v>325.88</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>190.1</v>
+        <v>292</v>
       </c>
       <c r="G2" t="n">
-        <v>798.88</v>
+        <v>181.09</v>
       </c>
       <c r="H2" t="n">
-        <v>258.88</v>
+        <v>105.64</v>
+      </c>
+      <c r="I2" t="n">
+        <v>473.09</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -492,26 +524,36 @@
           <t>P01</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>P01｜平鎮1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
-        <v>18</v>
-      </c>
-      <c r="D3" t="n">
-        <v>400</v>
-      </c>
       <c r="E3" t="n">
-        <v>323.02</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>188.43</v>
+        <v>312</v>
       </c>
       <c r="G3" t="n">
-        <v>723.02</v>
+        <v>152.56</v>
       </c>
       <c r="H3" t="n">
-        <v>183.02</v>
+        <v>88.98999999999999</v>
+      </c>
+      <c r="I3" t="n">
+        <v>464.56</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -520,26 +562,36 @@
           <t>P01</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>P01｜平鎮1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
-        <v>22</v>
-      </c>
-      <c r="D4" t="n">
-        <v>388</v>
-      </c>
       <c r="E4" t="n">
-        <v>384.5</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>224.29</v>
+        <v>252</v>
       </c>
       <c r="G4" t="n">
-        <v>772.5</v>
+        <v>227.02</v>
       </c>
       <c r="H4" t="n">
-        <v>232.5</v>
+        <v>132.43</v>
+      </c>
+      <c r="I4" t="n">
+        <v>479.02</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -548,26 +600,36 @@
           <t>P01</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>P01｜平鎮1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" t="n">
-        <v>26</v>
-      </c>
-      <c r="D5" t="n">
-        <v>428</v>
-      </c>
       <c r="E5" t="n">
-        <v>384.52</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
-        <v>224.3</v>
+        <v>284</v>
       </c>
       <c r="G5" t="n">
-        <v>812.52</v>
+        <v>194.82</v>
       </c>
       <c r="H5" t="n">
-        <v>272.52</v>
+        <v>113.65</v>
+      </c>
+      <c r="I5" t="n">
+        <v>478.82</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -576,26 +638,36 @@
           <t>P01</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>P01｜平鎮1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="C6" t="n">
-        <v>25</v>
-      </c>
-      <c r="D6" t="n">
-        <v>450</v>
-      </c>
       <c r="E6" t="n">
-        <v>345.14</v>
+        <v>8</v>
       </c>
       <c r="F6" t="n">
-        <v>201.33</v>
+        <v>314</v>
       </c>
       <c r="G6" t="n">
-        <v>795.14</v>
+        <v>201.22</v>
       </c>
       <c r="H6" t="n">
-        <v>255.14</v>
+        <v>117.38</v>
+      </c>
+      <c r="I6" t="n">
+        <v>515.22</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -604,26 +676,36 @@
           <t>P01</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>P01｜平鎮1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>6</v>
       </c>
-      <c r="C7" t="n">
-        <v>25</v>
-      </c>
-      <c r="D7" t="n">
-        <v>351</v>
-      </c>
       <c r="E7" t="n">
-        <v>388.55</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>226.65</v>
+        <v>191</v>
       </c>
       <c r="G7" t="n">
-        <v>739.55</v>
+        <v>275.89</v>
       </c>
       <c r="H7" t="n">
-        <v>199.55</v>
+        <v>160.94</v>
+      </c>
+      <c r="I7" t="n">
+        <v>466.89</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -632,26 +714,36 @@
           <t>P02</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>P02｜平鎮2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="n">
-        <v>31</v>
-      </c>
-      <c r="D8" t="n">
-        <v>439</v>
-      </c>
       <c r="E8" t="n">
-        <v>364.99</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>212.91</v>
+        <v>231</v>
       </c>
       <c r="G8" t="n">
-        <v>803.99</v>
+        <v>230.28</v>
       </c>
       <c r="H8" t="n">
-        <v>263.99</v>
+        <v>134.33</v>
+      </c>
+      <c r="I8" t="n">
+        <v>461.28</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -660,26 +752,36 @@
           <t>P02</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>P02｜平鎮2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>2</v>
       </c>
-      <c r="C9" t="n">
-        <v>26</v>
-      </c>
-      <c r="D9" t="n">
-        <v>376</v>
-      </c>
       <c r="E9" t="n">
-        <v>435.71</v>
+        <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>254.16</v>
+        <v>216</v>
       </c>
       <c r="G9" t="n">
-        <v>811.71</v>
+        <v>216.1</v>
       </c>
       <c r="H9" t="n">
-        <v>271.71</v>
+        <v>126.06</v>
+      </c>
+      <c r="I9" t="n">
+        <v>432.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -688,26 +790,36 @@
           <t>P02</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>P02｜平鎮2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>3</v>
       </c>
-      <c r="C10" t="n">
-        <v>25</v>
-      </c>
-      <c r="D10" t="n">
-        <v>344</v>
-      </c>
       <c r="E10" t="n">
-        <v>392.93</v>
+        <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>229.21</v>
+        <v>192</v>
       </c>
       <c r="G10" t="n">
-        <v>736.9299999999999</v>
+        <v>224.48</v>
       </c>
       <c r="H10" t="n">
-        <v>196.93</v>
+        <v>130.94</v>
+      </c>
+      <c r="I10" t="n">
+        <v>416.48</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -716,26 +828,36 @@
           <t>P02</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>P02｜平鎮2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>4</v>
       </c>
-      <c r="C11" t="n">
-        <v>28</v>
-      </c>
-      <c r="D11" t="n">
-        <v>436</v>
-      </c>
       <c r="E11" t="n">
-        <v>382.15</v>
+        <v>9</v>
       </c>
       <c r="F11" t="n">
-        <v>222.92</v>
+        <v>284</v>
       </c>
       <c r="G11" t="n">
-        <v>818.15</v>
+        <v>137.89</v>
       </c>
       <c r="H11" t="n">
-        <v>278.15</v>
+        <v>80.43000000000001</v>
+      </c>
+      <c r="I11" t="n">
+        <v>421.89</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -744,26 +866,36 @@
           <t>P02</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>P02｜平鎮2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>5</v>
       </c>
-      <c r="C12" t="n">
-        <v>24</v>
-      </c>
-      <c r="D12" t="n">
-        <v>364</v>
-      </c>
       <c r="E12" t="n">
-        <v>355.94</v>
+        <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>207.63</v>
+        <v>212</v>
       </c>
       <c r="G12" t="n">
-        <v>719.9400000000001</v>
+        <v>252.62</v>
       </c>
       <c r="H12" t="n">
-        <v>179.94</v>
+        <v>147.36</v>
+      </c>
+      <c r="I12" t="n">
+        <v>464.62</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -772,26 +904,36 @@
           <t>P02</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>P02｜平鎮2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>6</v>
       </c>
-      <c r="C13" t="n">
-        <v>27</v>
-      </c>
-      <c r="D13" t="n">
-        <v>368</v>
-      </c>
       <c r="E13" t="n">
-        <v>419.45</v>
+        <v>7</v>
       </c>
       <c r="F13" t="n">
-        <v>244.68</v>
+        <v>208</v>
       </c>
       <c r="G13" t="n">
-        <v>787.45</v>
+        <v>299.67</v>
       </c>
       <c r="H13" t="n">
-        <v>247.45</v>
+        <v>174.81</v>
+      </c>
+      <c r="I13" t="n">
+        <v>507.67</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -800,26 +942,36 @@
           <t>P03</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>P03｜平鎮3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>1</v>
       </c>
-      <c r="C14" t="n">
-        <v>27</v>
-      </c>
-      <c r="D14" t="n">
-        <v>388</v>
-      </c>
       <c r="E14" t="n">
-        <v>311.4</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>181.65</v>
+        <v>220</v>
       </c>
       <c r="G14" t="n">
-        <v>699.4</v>
+        <v>228.33</v>
       </c>
       <c r="H14" t="n">
-        <v>159.4</v>
+        <v>133.19</v>
+      </c>
+      <c r="I14" t="n">
+        <v>448.33</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -828,26 +980,36 @@
           <t>P03</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>P03｜平鎮3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>2</v>
       </c>
-      <c r="C15" t="n">
-        <v>23</v>
-      </c>
-      <c r="D15" t="n">
-        <v>356</v>
-      </c>
       <c r="E15" t="n">
-        <v>371.48</v>
+        <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>216.7</v>
+        <v>220</v>
       </c>
       <c r="G15" t="n">
-        <v>727.48</v>
+        <v>210.98</v>
       </c>
       <c r="H15" t="n">
-        <v>187.48</v>
+        <v>123.07</v>
+      </c>
+      <c r="I15" t="n">
+        <v>430.98</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -856,26 +1018,36 @@
           <t>P03</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>P03｜平鎮3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>3</v>
       </c>
-      <c r="C16" t="n">
-        <v>30</v>
-      </c>
-      <c r="D16" t="n">
-        <v>411</v>
-      </c>
       <c r="E16" t="n">
-        <v>354.36</v>
+        <v>8</v>
       </c>
       <c r="F16" t="n">
-        <v>206.71</v>
+        <v>235</v>
       </c>
       <c r="G16" t="n">
-        <v>765.36</v>
+        <v>207.93</v>
       </c>
       <c r="H16" t="n">
-        <v>225.36</v>
+        <v>121.29</v>
+      </c>
+      <c r="I16" t="n">
+        <v>442.93</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -884,26 +1056,36 @@
           <t>P03</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>P03｜平鎮3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>4</v>
       </c>
-      <c r="C17" t="n">
-        <v>23</v>
-      </c>
-      <c r="D17" t="n">
-        <v>341</v>
-      </c>
       <c r="E17" t="n">
-        <v>371.93</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>216.96</v>
+        <v>205</v>
       </c>
       <c r="G17" t="n">
-        <v>712.9299999999999</v>
+        <v>189.66</v>
       </c>
       <c r="H17" t="n">
-        <v>172.93</v>
+        <v>110.63</v>
+      </c>
+      <c r="I17" t="n">
+        <v>394.66</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -912,26 +1094,36 @@
           <t>P03</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>P03｜平鎮3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>5</v>
       </c>
-      <c r="C18" t="n">
-        <v>29</v>
-      </c>
-      <c r="D18" t="n">
-        <v>384</v>
-      </c>
       <c r="E18" t="n">
-        <v>358.56</v>
+        <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>209.16</v>
+        <v>216</v>
       </c>
       <c r="G18" t="n">
-        <v>742.5599999999999</v>
+        <v>270.63</v>
       </c>
       <c r="H18" t="n">
-        <v>202.56</v>
+        <v>157.87</v>
+      </c>
+      <c r="I18" t="n">
+        <v>486.63</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -940,26 +1132,36 @@
           <t>P03</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>P03｜平鎮3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>6</v>
       </c>
-      <c r="C19" t="n">
-        <v>29</v>
-      </c>
-      <c r="D19" t="n">
-        <v>432</v>
-      </c>
       <c r="E19" t="n">
-        <v>326.22</v>
+        <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>190.29</v>
+        <v>280</v>
       </c>
       <c r="G19" t="n">
-        <v>758.22</v>
+        <v>179.09</v>
       </c>
       <c r="H19" t="n">
-        <v>218.22</v>
+        <v>104.47</v>
+      </c>
+      <c r="I19" t="n">
+        <v>459.09</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -968,26 +1170,36 @@
           <t>P04</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>P04｜平鎮4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>1</v>
       </c>
-      <c r="C20" t="n">
-        <v>33</v>
-      </c>
-      <c r="D20" t="n">
-        <v>456</v>
-      </c>
       <c r="E20" t="n">
-        <v>428.57</v>
+        <v>9</v>
       </c>
       <c r="F20" t="n">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="G20" t="n">
-        <v>884.5700000000001</v>
+        <v>241.86</v>
       </c>
       <c r="H20" t="n">
-        <v>344.57</v>
+        <v>141.09</v>
+      </c>
+      <c r="I20" t="n">
+        <v>505.86</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -996,26 +1208,36 @@
           <t>P04</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>P04｜平鎮4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>2</v>
       </c>
-      <c r="C21" t="n">
-        <v>31</v>
-      </c>
-      <c r="D21" t="n">
-        <v>435</v>
-      </c>
       <c r="E21" t="n">
-        <v>376.41</v>
+        <v>11</v>
       </c>
       <c r="F21" t="n">
-        <v>219.57</v>
+        <v>275</v>
       </c>
       <c r="G21" t="n">
-        <v>811.41</v>
+        <v>231.68</v>
       </c>
       <c r="H21" t="n">
-        <v>271.41</v>
+        <v>135.14</v>
+      </c>
+      <c r="I21" t="n">
+        <v>506.68</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1024,26 +1246,36 @@
           <t>P04</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>P04｜平鎮4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>3</v>
       </c>
-      <c r="C22" t="n">
-        <v>25</v>
-      </c>
-      <c r="D22" t="n">
-        <v>322</v>
-      </c>
       <c r="E22" t="n">
-        <v>354.15</v>
+        <v>9</v>
       </c>
       <c r="F22" t="n">
-        <v>206.58</v>
+        <v>194</v>
       </c>
       <c r="G22" t="n">
-        <v>676.15</v>
+        <v>206.26</v>
       </c>
       <c r="H22" t="n">
-        <v>136.15</v>
+        <v>120.32</v>
+      </c>
+      <c r="I22" t="n">
+        <v>400.26</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1052,26 +1284,36 @@
           <t>P04</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>P04｜平鎮4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>4</v>
       </c>
-      <c r="C23" t="n">
-        <v>23</v>
-      </c>
-      <c r="D23" t="n">
-        <v>320</v>
-      </c>
       <c r="E23" t="n">
-        <v>380.67</v>
+        <v>7</v>
       </c>
       <c r="F23" t="n">
-        <v>222.06</v>
+        <v>192</v>
       </c>
       <c r="G23" t="n">
-        <v>700.67</v>
+        <v>213.52</v>
       </c>
       <c r="H23" t="n">
-        <v>160.67</v>
+        <v>124.55</v>
+      </c>
+      <c r="I23" t="n">
+        <v>405.52</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1080,26 +1322,36 @@
           <t>P04</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>P04｜平鎮4</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>5</v>
       </c>
-      <c r="C24" t="n">
-        <v>32</v>
-      </c>
-      <c r="D24" t="n">
-        <v>423</v>
-      </c>
       <c r="E24" t="n">
-        <v>391.04</v>
+        <v>10</v>
       </c>
       <c r="F24" t="n">
-        <v>228.11</v>
+        <v>247</v>
       </c>
       <c r="G24" t="n">
-        <v>814.04</v>
+        <v>201.42</v>
       </c>
       <c r="H24" t="n">
-        <v>274.04</v>
+        <v>117.49</v>
+      </c>
+      <c r="I24" t="n">
+        <v>448.42</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1108,26 +1360,36 @@
           <t>P04</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>P04｜平鎮4</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>6</v>
       </c>
-      <c r="C25" t="n">
-        <v>33</v>
-      </c>
-      <c r="D25" t="n">
-        <v>370</v>
-      </c>
       <c r="E25" t="n">
-        <v>427.59</v>
+        <v>7</v>
       </c>
       <c r="F25" t="n">
-        <v>249.43</v>
+        <v>162</v>
       </c>
       <c r="G25" t="n">
-        <v>797.59</v>
+        <v>287.71</v>
       </c>
       <c r="H25" t="n">
-        <v>257.59</v>
+        <v>167.83</v>
+      </c>
+      <c r="I25" t="n">
+        <v>449.71</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1136,26 +1398,36 @@
           <t>P05</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>P05｜平鎮5</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>1</v>
       </c>
-      <c r="C26" t="n">
-        <v>24</v>
-      </c>
-      <c r="D26" t="n">
-        <v>288</v>
-      </c>
       <c r="E26" t="n">
-        <v>388.88</v>
+        <v>7</v>
       </c>
       <c r="F26" t="n">
-        <v>226.85</v>
+        <v>152</v>
       </c>
       <c r="G26" t="n">
-        <v>676.88</v>
+        <v>274.25</v>
       </c>
       <c r="H26" t="n">
-        <v>136.88</v>
+        <v>159.98</v>
+      </c>
+      <c r="I26" t="n">
+        <v>426.25</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1164,26 +1436,36 @@
           <t>P05</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>P05｜平鎮5</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>2</v>
       </c>
-      <c r="C27" t="n">
-        <v>29</v>
-      </c>
-      <c r="D27" t="n">
-        <v>408</v>
-      </c>
       <c r="E27" t="n">
-        <v>339.73</v>
+        <v>11</v>
       </c>
       <c r="F27" t="n">
-        <v>198.17</v>
+        <v>264</v>
       </c>
       <c r="G27" t="n">
-        <v>747.73</v>
+        <v>270.49</v>
       </c>
       <c r="H27" t="n">
-        <v>207.73</v>
+        <v>157.79</v>
+      </c>
+      <c r="I27" t="n">
+        <v>534.49</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1192,26 +1474,36 @@
           <t>P05</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>P05｜平鎮5</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>3</v>
       </c>
-      <c r="C28" t="n">
-        <v>31</v>
-      </c>
-      <c r="D28" t="n">
-        <v>408</v>
-      </c>
       <c r="E28" t="n">
-        <v>358.1</v>
+        <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>208.89</v>
+        <v>248</v>
       </c>
       <c r="G28" t="n">
-        <v>766.1</v>
+        <v>227.03</v>
       </c>
       <c r="H28" t="n">
-        <v>226.1</v>
+        <v>132.44</v>
+      </c>
+      <c r="I28" t="n">
+        <v>475.03</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1220,26 +1512,36 @@
           <t>P05</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>P05｜平鎮5</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>4</v>
       </c>
-      <c r="C29" t="n">
-        <v>32</v>
-      </c>
-      <c r="D29" t="n">
-        <v>408</v>
-      </c>
       <c r="E29" t="n">
-        <v>409.74</v>
+        <v>11</v>
       </c>
       <c r="F29" t="n">
-        <v>239.01</v>
+        <v>240</v>
       </c>
       <c r="G29" t="n">
-        <v>817.74</v>
+        <v>198.15</v>
       </c>
       <c r="H29" t="n">
-        <v>277.74</v>
+        <v>115.59</v>
+      </c>
+      <c r="I29" t="n">
+        <v>438.15</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1248,26 +1550,36 @@
           <t>P05</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P05｜平鎮5</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>5</v>
       </c>
-      <c r="C30" t="n">
-        <v>34</v>
-      </c>
-      <c r="D30" t="n">
-        <v>408</v>
-      </c>
       <c r="E30" t="n">
-        <v>438.47</v>
+        <v>10</v>
       </c>
       <c r="F30" t="n">
-        <v>255.77</v>
+        <v>216</v>
       </c>
       <c r="G30" t="n">
-        <v>846.47</v>
+        <v>297.69</v>
       </c>
       <c r="H30" t="n">
-        <v>306.47</v>
+        <v>173.65</v>
+      </c>
+      <c r="I30" t="n">
+        <v>513.6900000000001</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1276,26 +1588,36 @@
           <t>P05</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P05｜平鎮5</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>6</v>
       </c>
-      <c r="C31" t="n">
-        <v>27</v>
-      </c>
-      <c r="D31" t="n">
-        <v>368</v>
-      </c>
       <c r="E31" t="n">
-        <v>398.12</v>
+        <v>10</v>
       </c>
       <c r="F31" t="n">
-        <v>232.24</v>
+        <v>232</v>
       </c>
       <c r="G31" t="n">
-        <v>766.12</v>
+        <v>295.55</v>
       </c>
       <c r="H31" t="n">
-        <v>226.12</v>
+        <v>172.4</v>
+      </c>
+      <c r="I31" t="n">
+        <v>527.55</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1304,26 +1626,36 @@
           <t>P06</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P06｜平鎮6</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>1</v>
       </c>
-      <c r="C32" t="n">
-        <v>30</v>
-      </c>
-      <c r="D32" t="n">
-        <v>392</v>
-      </c>
       <c r="E32" t="n">
-        <v>413.96</v>
+        <v>11</v>
       </c>
       <c r="F32" t="n">
-        <v>241.48</v>
+        <v>240</v>
       </c>
       <c r="G32" t="n">
-        <v>805.96</v>
+        <v>312.65</v>
       </c>
       <c r="H32" t="n">
-        <v>265.96</v>
+        <v>182.38</v>
+      </c>
+      <c r="I32" t="n">
+        <v>552.65</v>
+      </c>
+      <c r="J32" t="n">
+        <v>12.65</v>
       </c>
     </row>
     <row r="33">
@@ -1332,26 +1664,36 @@
           <t>P06</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>P06｜平鎮6</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>2</v>
       </c>
-      <c r="C33" t="n">
-        <v>32</v>
-      </c>
-      <c r="D33" t="n">
-        <v>416</v>
-      </c>
       <c r="E33" t="n">
-        <v>313.78</v>
+        <v>11</v>
       </c>
       <c r="F33" t="n">
-        <v>183.04</v>
+        <v>248</v>
       </c>
       <c r="G33" t="n">
-        <v>729.78</v>
+        <v>256.08</v>
       </c>
       <c r="H33" t="n">
-        <v>189.78</v>
+        <v>149.38</v>
+      </c>
+      <c r="I33" t="n">
+        <v>504.08</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1360,26 +1702,36 @@
           <t>P06</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>P06｜平鎮6</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>3</v>
       </c>
-      <c r="C34" t="n">
-        <v>28</v>
-      </c>
-      <c r="D34" t="n">
-        <v>344</v>
-      </c>
       <c r="E34" t="n">
-        <v>477.84</v>
+        <v>8</v>
       </c>
       <c r="F34" t="n">
-        <v>278.74</v>
+        <v>184</v>
       </c>
       <c r="G34" t="n">
-        <v>821.84</v>
+        <v>362.43</v>
       </c>
       <c r="H34" t="n">
-        <v>281.84</v>
+        <v>211.42</v>
+      </c>
+      <c r="I34" t="n">
+        <v>546.4299999999999</v>
+      </c>
+      <c r="J34" t="n">
+        <v>6.43</v>
       </c>
     </row>
     <row r="35">
@@ -1388,26 +1740,36 @@
           <t>P06</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>P06｜平鎮6</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>4</v>
       </c>
-      <c r="C35" t="n">
-        <v>27</v>
-      </c>
-      <c r="D35" t="n">
-        <v>376</v>
-      </c>
       <c r="E35" t="n">
-        <v>372.98</v>
+        <v>11</v>
       </c>
       <c r="F35" t="n">
-        <v>217.57</v>
+        <v>248</v>
       </c>
       <c r="G35" t="n">
-        <v>748.98</v>
+        <v>195.19</v>
       </c>
       <c r="H35" t="n">
-        <v>208.98</v>
+        <v>113.86</v>
+      </c>
+      <c r="I35" t="n">
+        <v>443.19</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1416,26 +1778,36 @@
           <t>P06</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>P06｜平鎮6</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>5</v>
       </c>
-      <c r="C36" t="n">
-        <v>30</v>
-      </c>
-      <c r="D36" t="n">
-        <v>376</v>
-      </c>
       <c r="E36" t="n">
-        <v>405.72</v>
+        <v>10</v>
       </c>
       <c r="F36" t="n">
-        <v>236.67</v>
+        <v>216</v>
       </c>
       <c r="G36" t="n">
-        <v>781.72</v>
+        <v>271.29</v>
       </c>
       <c r="H36" t="n">
-        <v>241.72</v>
+        <v>158.25</v>
+      </c>
+      <c r="I36" t="n">
+        <v>487.29</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1444,26 +1816,36 @@
           <t>P06</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>P06｜平鎮6</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>6</v>
       </c>
-      <c r="C37" t="n">
-        <v>27</v>
-      </c>
-      <c r="D37" t="n">
-        <v>368</v>
-      </c>
       <c r="E37" t="n">
-        <v>377.06</v>
+        <v>10</v>
       </c>
       <c r="F37" t="n">
-        <v>219.95</v>
+        <v>232</v>
       </c>
       <c r="G37" t="n">
-        <v>745.0599999999999</v>
+        <v>276.47</v>
       </c>
       <c r="H37" t="n">
-        <v>205.06</v>
+        <v>161.28</v>
+      </c>
+      <c r="I37" t="n">
+        <v>508.47</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1472,26 +1854,36 @@
           <t>P07</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>P07｜平鎮7</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>1</v>
       </c>
-      <c r="C38" t="n">
-        <v>31</v>
-      </c>
-      <c r="D38" t="n">
-        <v>357</v>
-      </c>
       <c r="E38" t="n">
-        <v>424.87</v>
+        <v>7</v>
       </c>
       <c r="F38" t="n">
-        <v>247.84</v>
+        <v>165</v>
       </c>
       <c r="G38" t="n">
-        <v>781.87</v>
+        <v>276.15</v>
       </c>
       <c r="H38" t="n">
-        <v>241.87</v>
+        <v>161.09</v>
+      </c>
+      <c r="I38" t="n">
+        <v>441.15</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1500,26 +1892,36 @@
           <t>P07</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>P07｜平鎮7</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>2</v>
       </c>
-      <c r="C39" t="n">
-        <v>27</v>
-      </c>
-      <c r="D39" t="n">
-        <v>346</v>
-      </c>
       <c r="E39" t="n">
-        <v>291.52</v>
+        <v>9</v>
       </c>
       <c r="F39" t="n">
-        <v>170.05</v>
+        <v>202</v>
       </c>
       <c r="G39" t="n">
-        <v>637.52</v>
+        <v>193.01</v>
       </c>
       <c r="H39" t="n">
-        <v>97.52</v>
+        <v>112.59</v>
+      </c>
+      <c r="I39" t="n">
+        <v>395.01</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1528,26 +1930,36 @@
           <t>P07</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>P07｜平鎮7</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>3</v>
       </c>
-      <c r="C40" t="n">
-        <v>25</v>
-      </c>
-      <c r="D40" t="n">
-        <v>289</v>
-      </c>
       <c r="E40" t="n">
-        <v>355.34</v>
+        <v>8</v>
       </c>
       <c r="F40" t="n">
-        <v>207.28</v>
+        <v>153</v>
       </c>
       <c r="G40" t="n">
-        <v>644.34</v>
+        <v>272.04</v>
       </c>
       <c r="H40" t="n">
-        <v>104.34</v>
+        <v>158.69</v>
+      </c>
+      <c r="I40" t="n">
+        <v>425.04</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1556,26 +1968,36 @@
           <t>P07</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>P07｜平鎮7</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>4</v>
       </c>
-      <c r="C41" t="n">
-        <v>27</v>
-      </c>
-      <c r="D41" t="n">
-        <v>336</v>
-      </c>
       <c r="E41" t="n">
-        <v>477.46</v>
+        <v>10</v>
       </c>
       <c r="F41" t="n">
-        <v>278.52</v>
+        <v>200</v>
       </c>
       <c r="G41" t="n">
-        <v>813.46</v>
+        <v>342.41</v>
       </c>
       <c r="H41" t="n">
-        <v>273.46</v>
+        <v>199.74</v>
+      </c>
+      <c r="I41" t="n">
+        <v>542.41</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.41</v>
       </c>
     </row>
     <row r="42">
@@ -1584,26 +2006,36 @@
           <t>P07</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>P07｜平鎮7</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
         <v>5</v>
       </c>
-      <c r="C42" t="n">
-        <v>30</v>
-      </c>
-      <c r="D42" t="n">
-        <v>312</v>
-      </c>
       <c r="E42" t="n">
-        <v>451.59</v>
+        <v>7</v>
       </c>
       <c r="F42" t="n">
-        <v>263.42</v>
+        <v>128</v>
       </c>
       <c r="G42" t="n">
-        <v>763.59</v>
+        <v>289.58</v>
       </c>
       <c r="H42" t="n">
-        <v>223.59</v>
+        <v>168.92</v>
+      </c>
+      <c r="I42" t="n">
+        <v>417.58</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1612,26 +2044,36 @@
           <t>P07</t>
         </is>
       </c>
-      <c r="B43" t="n">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>P07｜平鎮7</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
         <v>6</v>
       </c>
-      <c r="C43" t="n">
-        <v>32</v>
-      </c>
-      <c r="D43" t="n">
-        <v>354</v>
-      </c>
       <c r="E43" t="n">
-        <v>481.58</v>
+        <v>8</v>
       </c>
       <c r="F43" t="n">
-        <v>280.92</v>
+        <v>162</v>
       </c>
       <c r="G43" t="n">
-        <v>835.58</v>
+        <v>378.97</v>
       </c>
       <c r="H43" t="n">
-        <v>295.58</v>
+        <v>221.07</v>
+      </c>
+      <c r="I43" t="n">
+        <v>540.97</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.97</v>
       </c>
     </row>
     <row r="44">
@@ -1640,26 +2082,36 @@
           <t>P08</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>P08｜平鎮8</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
         <v>1</v>
       </c>
-      <c r="C44" t="n">
-        <v>24</v>
-      </c>
-      <c r="D44" t="n">
-        <v>277</v>
-      </c>
       <c r="E44" t="n">
-        <v>422.12</v>
+        <v>9</v>
       </c>
       <c r="F44" t="n">
-        <v>246.24</v>
+        <v>157</v>
       </c>
       <c r="G44" t="n">
-        <v>699.12</v>
+        <v>259.54</v>
       </c>
       <c r="H44" t="n">
-        <v>159.12</v>
+        <v>151.4</v>
+      </c>
+      <c r="I44" t="n">
+        <v>416.54</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1668,26 +2120,36 @@
           <t>P08</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>P08｜平鎮8</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
         <v>2</v>
       </c>
-      <c r="C45" t="n">
-        <v>27</v>
-      </c>
-      <c r="D45" t="n">
-        <v>324</v>
-      </c>
       <c r="E45" t="n">
-        <v>438.8</v>
+        <v>10</v>
       </c>
       <c r="F45" t="n">
-        <v>255.97</v>
+        <v>188</v>
       </c>
       <c r="G45" t="n">
-        <v>762.8</v>
+        <v>323.76</v>
       </c>
       <c r="H45" t="n">
-        <v>222.8</v>
+        <v>188.86</v>
+      </c>
+      <c r="I45" t="n">
+        <v>511.76</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1696,26 +2158,36 @@
           <t>P08</t>
         </is>
       </c>
-      <c r="B46" t="n">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>P08｜平鎮8</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
         <v>3</v>
       </c>
-      <c r="C46" t="n">
-        <v>33</v>
-      </c>
-      <c r="D46" t="n">
-        <v>356</v>
-      </c>
       <c r="E46" t="n">
-        <v>412.8</v>
+        <v>9</v>
       </c>
       <c r="F46" t="n">
-        <v>240.8</v>
+        <v>164</v>
       </c>
       <c r="G46" t="n">
-        <v>768.8</v>
+        <v>291.6</v>
       </c>
       <c r="H46" t="n">
-        <v>228.8</v>
+        <v>170.1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>455.6</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1724,26 +2196,36 @@
           <t>P08</t>
         </is>
       </c>
-      <c r="B47" t="n">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>P08｜平鎮8</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
         <v>4</v>
       </c>
-      <c r="C47" t="n">
-        <v>26</v>
-      </c>
-      <c r="D47" t="n">
-        <v>320</v>
-      </c>
       <c r="E47" t="n">
-        <v>375.63</v>
+        <v>10</v>
       </c>
       <c r="F47" t="n">
-        <v>219.12</v>
+        <v>192</v>
       </c>
       <c r="G47" t="n">
-        <v>695.63</v>
+        <v>298.18</v>
       </c>
       <c r="H47" t="n">
-        <v>155.63</v>
+        <v>173.94</v>
+      </c>
+      <c r="I47" t="n">
+        <v>490.18</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1752,26 +2234,36 @@
           <t>P08</t>
         </is>
       </c>
-      <c r="B48" t="n">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>P08｜平鎮8</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
         <v>5</v>
       </c>
-      <c r="C48" t="n">
-        <v>27</v>
-      </c>
-      <c r="D48" t="n">
-        <v>344</v>
-      </c>
       <c r="E48" t="n">
-        <v>424.56</v>
+        <v>11</v>
       </c>
       <c r="F48" t="n">
-        <v>247.66</v>
+        <v>216</v>
       </c>
       <c r="G48" t="n">
-        <v>768.5599999999999</v>
+        <v>272.54</v>
       </c>
       <c r="H48" t="n">
-        <v>228.56</v>
+        <v>158.98</v>
+      </c>
+      <c r="I48" t="n">
+        <v>488.54</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1780,26 +2272,36 @@
           <t>P08</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>P08｜平鎮8</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
         <v>6</v>
       </c>
-      <c r="C49" t="n">
-        <v>30</v>
-      </c>
-      <c r="D49" t="n">
-        <v>368</v>
-      </c>
       <c r="E49" t="n">
-        <v>397.76</v>
+        <v>11</v>
       </c>
       <c r="F49" t="n">
-        <v>232.02</v>
+        <v>216</v>
       </c>
       <c r="G49" t="n">
-        <v>765.76</v>
+        <v>303.29</v>
       </c>
       <c r="H49" t="n">
-        <v>225.76</v>
+        <v>176.92</v>
+      </c>
+      <c r="I49" t="n">
+        <v>519.29</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1808,26 +2310,36 @@
           <t>P09</t>
         </is>
       </c>
-      <c r="B50" t="n">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>P09｜平鎮9</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
         <v>1</v>
       </c>
-      <c r="C50" t="n">
-        <v>28</v>
-      </c>
-      <c r="D50" t="n">
-        <v>339</v>
-      </c>
       <c r="E50" t="n">
-        <v>415.12</v>
+        <v>11</v>
       </c>
       <c r="F50" t="n">
-        <v>242.15</v>
+        <v>203</v>
       </c>
       <c r="G50" t="n">
-        <v>754.12</v>
+        <v>282.72</v>
       </c>
       <c r="H50" t="n">
-        <v>214.12</v>
+        <v>164.92</v>
+      </c>
+      <c r="I50" t="n">
+        <v>485.72</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1836,26 +2348,36 @@
           <t>P09</t>
         </is>
       </c>
-      <c r="B51" t="n">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>P09｜平鎮9</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
         <v>2</v>
       </c>
-      <c r="C51" t="n">
-        <v>28</v>
-      </c>
-      <c r="D51" t="n">
-        <v>314.5</v>
-      </c>
       <c r="E51" t="n">
-        <v>368.64</v>
+        <v>10</v>
       </c>
       <c r="F51" t="n">
-        <v>215.04</v>
+        <v>170.5</v>
       </c>
       <c r="G51" t="n">
-        <v>683.14</v>
+        <v>249.72</v>
       </c>
       <c r="H51" t="n">
-        <v>143.14</v>
+        <v>145.67</v>
+      </c>
+      <c r="I51" t="n">
+        <v>420.22</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1864,26 +2386,36 @@
           <t>P09</t>
         </is>
       </c>
-      <c r="B52" t="n">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>P09｜平鎮9</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
         <v>3</v>
       </c>
-      <c r="C52" t="n">
-        <v>34</v>
-      </c>
-      <c r="D52" t="n">
-        <v>362</v>
-      </c>
       <c r="E52" t="n">
-        <v>453.19</v>
+        <v>11</v>
       </c>
       <c r="F52" t="n">
-        <v>264.36</v>
+        <v>178</v>
       </c>
       <c r="G52" t="n">
-        <v>815.1900000000001</v>
+        <v>385.14</v>
       </c>
       <c r="H52" t="n">
-        <v>275.19</v>
+        <v>224.66</v>
+      </c>
+      <c r="I52" t="n">
+        <v>563.14</v>
+      </c>
+      <c r="J52" t="n">
+        <v>23.14</v>
       </c>
     </row>
     <row r="53">
@@ -1892,26 +2424,36 @@
           <t>P09</t>
         </is>
       </c>
-      <c r="B53" t="n">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>P09｜平鎮9</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
         <v>4</v>
       </c>
-      <c r="C53" t="n">
-        <v>24</v>
-      </c>
-      <c r="D53" t="n">
-        <v>232</v>
-      </c>
       <c r="E53" t="n">
-        <v>432.29</v>
+        <v>6</v>
       </c>
       <c r="F53" t="n">
-        <v>252.17</v>
+        <v>88</v>
       </c>
       <c r="G53" t="n">
-        <v>664.29</v>
+        <v>364.92</v>
       </c>
       <c r="H53" t="n">
-        <v>124.29</v>
+        <v>212.87</v>
+      </c>
+      <c r="I53" t="n">
+        <v>452.92</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1920,26 +2462,36 @@
           <t>P09</t>
         </is>
       </c>
-      <c r="B54" t="n">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>P09｜平鎮9</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
         <v>5</v>
       </c>
-      <c r="C54" t="n">
-        <v>29</v>
-      </c>
-      <c r="D54" t="n">
-        <v>320</v>
-      </c>
       <c r="E54" t="n">
-        <v>369.54</v>
+        <v>12</v>
       </c>
       <c r="F54" t="n">
-        <v>215.56</v>
+        <v>184</v>
       </c>
       <c r="G54" t="n">
-        <v>689.54</v>
+        <v>233.71</v>
       </c>
       <c r="H54" t="n">
-        <v>149.54</v>
+        <v>136.33</v>
+      </c>
+      <c r="I54" t="n">
+        <v>417.71</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1948,26 +2500,36 @@
           <t>P09</t>
         </is>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>P09｜平鎮9</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
         <v>6</v>
       </c>
-      <c r="C55" t="n">
-        <v>34</v>
-      </c>
-      <c r="D55" t="n">
-        <v>376</v>
-      </c>
       <c r="E55" t="n">
-        <v>331.33</v>
+        <v>14</v>
       </c>
       <c r="F55" t="n">
-        <v>193.28</v>
+        <v>216</v>
       </c>
       <c r="G55" t="n">
-        <v>707.33</v>
+        <v>200</v>
       </c>
       <c r="H55" t="n">
-        <v>167.33</v>
+        <v>116.67</v>
+      </c>
+      <c r="I55" t="n">
+        <v>416</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -1976,26 +2538,36 @@
           <t>P10</t>
         </is>
       </c>
-      <c r="B56" t="n">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>P10｜平鎮10</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
         <v>1</v>
       </c>
-      <c r="C56" t="n">
-        <v>26</v>
-      </c>
-      <c r="D56" t="n">
-        <v>248</v>
-      </c>
       <c r="E56" t="n">
-        <v>505.71</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
-        <v>295</v>
+        <v>88</v>
       </c>
       <c r="G56" t="n">
-        <v>753.71</v>
+        <v>345.28</v>
       </c>
       <c r="H56" t="n">
-        <v>213.71</v>
+        <v>201.41</v>
+      </c>
+      <c r="I56" t="n">
+        <v>433.28</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2004,26 +2576,36 @@
           <t>P10</t>
         </is>
       </c>
-      <c r="B57" t="n">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>P10｜平鎮10</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
         <v>2</v>
       </c>
-      <c r="C57" t="n">
-        <v>27</v>
-      </c>
-      <c r="D57" t="n">
-        <v>264</v>
-      </c>
       <c r="E57" t="n">
-        <v>530.42</v>
+        <v>7</v>
       </c>
       <c r="F57" t="n">
-        <v>309.41</v>
+        <v>104</v>
       </c>
       <c r="G57" t="n">
-        <v>794.42</v>
+        <v>327.75</v>
       </c>
       <c r="H57" t="n">
-        <v>254.42</v>
+        <v>191.19</v>
+      </c>
+      <c r="I57" t="n">
+        <v>431.75</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -2032,26 +2614,36 @@
           <t>P10</t>
         </is>
       </c>
-      <c r="B58" t="n">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>P10｜平鎮10</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
         <v>3</v>
       </c>
-      <c r="C58" t="n">
-        <v>36</v>
-      </c>
-      <c r="D58" t="n">
-        <v>352</v>
-      </c>
       <c r="E58" t="n">
-        <v>321.67</v>
+        <v>9</v>
       </c>
       <c r="F58" t="n">
-        <v>187.64</v>
+        <v>136</v>
       </c>
       <c r="G58" t="n">
-        <v>673.67</v>
+        <v>234.67</v>
       </c>
       <c r="H58" t="n">
-        <v>133.67</v>
+        <v>136.89</v>
+      </c>
+      <c r="I58" t="n">
+        <v>370.67</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -2060,26 +2652,36 @@
           <t>P10</t>
         </is>
       </c>
-      <c r="B59" t="n">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>P10｜平鎮10</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
         <v>4</v>
       </c>
-      <c r="C59" t="n">
-        <v>31</v>
-      </c>
-      <c r="D59" t="n">
-        <v>320</v>
-      </c>
       <c r="E59" t="n">
-        <v>334.33</v>
+        <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>195.03</v>
+        <v>152</v>
       </c>
       <c r="G59" t="n">
-        <v>654.33</v>
+        <v>208.37</v>
       </c>
       <c r="H59" t="n">
-        <v>114.33</v>
+        <v>121.55</v>
+      </c>
+      <c r="I59" t="n">
+        <v>360.37</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2088,26 +2690,36 @@
           <t>P10</t>
         </is>
       </c>
-      <c r="B60" t="n">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>P10｜平鎮10</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
         <v>5</v>
       </c>
-      <c r="C60" t="n">
-        <v>28</v>
-      </c>
-      <c r="D60" t="n">
-        <v>296</v>
-      </c>
       <c r="E60" t="n">
-        <v>393.11</v>
+        <v>10</v>
       </c>
       <c r="F60" t="n">
-        <v>229.31</v>
+        <v>152</v>
       </c>
       <c r="G60" t="n">
-        <v>689.11</v>
+        <v>204.71</v>
       </c>
       <c r="H60" t="n">
-        <v>149.11</v>
+        <v>119.41</v>
+      </c>
+      <c r="I60" t="n">
+        <v>356.71</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -2116,26 +2728,36 @@
           <t>P10</t>
         </is>
       </c>
-      <c r="B61" t="n">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>P10｜平鎮10</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
         <v>6</v>
       </c>
-      <c r="C61" t="n">
-        <v>31</v>
-      </c>
-      <c r="D61" t="n">
-        <v>312</v>
-      </c>
       <c r="E61" t="n">
-        <v>345.62</v>
+        <v>9</v>
       </c>
       <c r="F61" t="n">
-        <v>201.61</v>
+        <v>136</v>
       </c>
       <c r="G61" t="n">
-        <v>657.62</v>
+        <v>212.76</v>
       </c>
       <c r="H61" t="n">
-        <v>117.62</v>
+        <v>124.11</v>
+      </c>
+      <c r="I61" t="n">
+        <v>348.76</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2144,26 +2766,36 @@
           <t>P11</t>
         </is>
       </c>
-      <c r="B62" t="n">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>P11｜平鎮11</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
         <v>1</v>
       </c>
-      <c r="C62" t="n">
-        <v>16</v>
-      </c>
-      <c r="D62" t="n">
-        <v>176</v>
-      </c>
       <c r="E62" t="n">
-        <v>513.08</v>
+        <v>7</v>
       </c>
       <c r="F62" t="n">
-        <v>299.3</v>
+        <v>104</v>
       </c>
       <c r="G62" t="n">
-        <v>689.08</v>
+        <v>314.1</v>
       </c>
       <c r="H62" t="n">
-        <v>149.08</v>
+        <v>183.22</v>
+      </c>
+      <c r="I62" t="n">
+        <v>418.1</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -2172,26 +2804,36 @@
           <t>P11</t>
         </is>
       </c>
-      <c r="B63" t="n">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>P11｜平鎮11</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
         <v>2</v>
       </c>
-      <c r="C63" t="n">
-        <v>30</v>
-      </c>
-      <c r="D63" t="n">
-        <v>352</v>
-      </c>
       <c r="E63" t="n">
-        <v>324.91</v>
+        <v>15</v>
       </c>
       <c r="F63" t="n">
-        <v>189.53</v>
+        <v>232</v>
       </c>
       <c r="G63" t="n">
-        <v>676.91</v>
+        <v>151.97</v>
       </c>
       <c r="H63" t="n">
-        <v>136.91</v>
+        <v>88.65000000000001</v>
+      </c>
+      <c r="I63" t="n">
+        <v>383.97</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -2200,26 +2842,36 @@
           <t>P11</t>
         </is>
       </c>
-      <c r="B64" t="n">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>P11｜平鎮11</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
         <v>3</v>
       </c>
-      <c r="C64" t="n">
-        <v>30</v>
-      </c>
-      <c r="D64" t="n">
-        <v>296</v>
-      </c>
       <c r="E64" t="n">
-        <v>393.64</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
-        <v>229.62</v>
+        <v>120</v>
       </c>
       <c r="G64" t="n">
-        <v>689.64</v>
+        <v>305.63</v>
       </c>
       <c r="H64" t="n">
-        <v>149.64</v>
+        <v>178.29</v>
+      </c>
+      <c r="I64" t="n">
+        <v>425.63</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2228,26 +2880,36 @@
           <t>P11</t>
         </is>
       </c>
-      <c r="B65" t="n">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>P11｜平鎮11</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
         <v>4</v>
       </c>
-      <c r="C65" t="n">
-        <v>25</v>
-      </c>
-      <c r="D65" t="n">
-        <v>272</v>
-      </c>
       <c r="E65" t="n">
-        <v>427.74</v>
+        <v>10</v>
       </c>
       <c r="F65" t="n">
-        <v>249.52</v>
+        <v>152</v>
       </c>
       <c r="G65" t="n">
-        <v>699.74</v>
+        <v>276.1</v>
       </c>
       <c r="H65" t="n">
-        <v>159.74</v>
+        <v>161.06</v>
+      </c>
+      <c r="I65" t="n">
+        <v>428.1</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2256,26 +2918,36 @@
           <t>P11</t>
         </is>
       </c>
-      <c r="B66" t="n">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>P11｜平鎮11</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
         <v>5</v>
       </c>
-      <c r="C66" t="n">
-        <v>32</v>
-      </c>
-      <c r="D66" t="n">
-        <v>368</v>
-      </c>
       <c r="E66" t="n">
-        <v>367.94</v>
+        <v>15</v>
       </c>
       <c r="F66" t="n">
-        <v>214.63</v>
+        <v>232</v>
       </c>
       <c r="G66" t="n">
-        <v>735.9400000000001</v>
+        <v>202.43</v>
       </c>
       <c r="H66" t="n">
-        <v>195.94</v>
+        <v>118.08</v>
+      </c>
+      <c r="I66" t="n">
+        <v>434.43</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2284,26 +2956,36 @@
           <t>P11</t>
         </is>
       </c>
-      <c r="B67" t="n">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>P11｜平鎮11</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
         <v>6</v>
       </c>
-      <c r="C67" t="n">
-        <v>30</v>
-      </c>
-      <c r="D67" t="n">
-        <v>336</v>
-      </c>
       <c r="E67" t="n">
-        <v>322.63</v>
+        <v>13</v>
       </c>
       <c r="F67" t="n">
-        <v>188.2</v>
+        <v>200</v>
       </c>
       <c r="G67" t="n">
-        <v>658.63</v>
+        <v>191.39</v>
       </c>
       <c r="H67" t="n">
-        <v>118.63</v>
+        <v>111.65</v>
+      </c>
+      <c r="I67" t="n">
+        <v>391.39</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -2312,26 +2994,36 @@
           <t>P12</t>
         </is>
       </c>
-      <c r="B68" t="n">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>P12｜平鎮12</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
         <v>1</v>
       </c>
-      <c r="C68" t="n">
-        <v>27</v>
-      </c>
-      <c r="D68" t="n">
-        <v>280</v>
-      </c>
       <c r="E68" t="n">
-        <v>423.22</v>
+        <v>9</v>
       </c>
       <c r="F68" t="n">
-        <v>246.88</v>
+        <v>136</v>
       </c>
       <c r="G68" t="n">
-        <v>703.22</v>
+        <v>262.02</v>
       </c>
       <c r="H68" t="n">
-        <v>163.22</v>
+        <v>152.84</v>
+      </c>
+      <c r="I68" t="n">
+        <v>398.02</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -2340,26 +3032,36 @@
           <t>P12</t>
         </is>
       </c>
-      <c r="B69" t="n">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>P12｜平鎮12</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
         <v>2</v>
       </c>
-      <c r="C69" t="n">
-        <v>34</v>
-      </c>
-      <c r="D69" t="n">
-        <v>360</v>
-      </c>
       <c r="E69" t="n">
-        <v>301.17</v>
+        <v>12</v>
       </c>
       <c r="F69" t="n">
-        <v>175.69</v>
+        <v>184</v>
       </c>
       <c r="G69" t="n">
-        <v>661.17</v>
+        <v>187.49</v>
       </c>
       <c r="H69" t="n">
-        <v>121.17</v>
+        <v>109.37</v>
+      </c>
+      <c r="I69" t="n">
+        <v>371.49</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2368,26 +3070,36 @@
           <t>P12</t>
         </is>
       </c>
-      <c r="B70" t="n">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>P12｜平鎮12</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
         <v>3</v>
       </c>
-      <c r="C70" t="n">
-        <v>27</v>
-      </c>
-      <c r="D70" t="n">
-        <v>304</v>
-      </c>
       <c r="E70" t="n">
-        <v>440.36</v>
+        <v>12</v>
       </c>
       <c r="F70" t="n">
-        <v>256.87</v>
+        <v>184</v>
       </c>
       <c r="G70" t="n">
-        <v>744.36</v>
+        <v>299.27</v>
       </c>
       <c r="H70" t="n">
-        <v>204.36</v>
+        <v>174.58</v>
+      </c>
+      <c r="I70" t="n">
+        <v>483.27</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2396,26 +3108,36 @@
           <t>P12</t>
         </is>
       </c>
-      <c r="B71" t="n">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>P12｜平鎮12</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
         <v>4</v>
       </c>
-      <c r="C71" t="n">
-        <v>29</v>
-      </c>
-      <c r="D71" t="n">
-        <v>312</v>
-      </c>
       <c r="E71" t="n">
-        <v>404.86</v>
+        <v>11</v>
       </c>
       <c r="F71" t="n">
-        <v>236.17</v>
+        <v>168</v>
       </c>
       <c r="G71" t="n">
-        <v>716.86</v>
+        <v>299.58</v>
       </c>
       <c r="H71" t="n">
-        <v>176.86</v>
+        <v>174.75</v>
+      </c>
+      <c r="I71" t="n">
+        <v>467.58</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -2424,26 +3146,36 @@
           <t>P12</t>
         </is>
       </c>
-      <c r="B72" t="n">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>P12｜平鎮12</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
         <v>5</v>
       </c>
-      <c r="C72" t="n">
-        <v>26</v>
-      </c>
-      <c r="D72" t="n">
-        <v>263</v>
-      </c>
       <c r="E72" t="n">
-        <v>495.53</v>
+        <v>8</v>
       </c>
       <c r="F72" t="n">
-        <v>289.06</v>
+        <v>120</v>
       </c>
       <c r="G72" t="n">
-        <v>758.53</v>
+        <v>286.26</v>
       </c>
       <c r="H72" t="n">
-        <v>218.53</v>
+        <v>166.99</v>
+      </c>
+      <c r="I72" t="n">
+        <v>406.26</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2452,26 +3184,36 @@
           <t>P12</t>
         </is>
       </c>
-      <c r="B73" t="n">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>P12｜平鎮12</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
         <v>6</v>
       </c>
-      <c r="C73" t="n">
-        <v>29</v>
-      </c>
-      <c r="D73" t="n">
-        <v>280</v>
-      </c>
       <c r="E73" t="n">
-        <v>383.69</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
-        <v>223.82</v>
+        <v>104</v>
       </c>
       <c r="G73" t="n">
-        <v>663.6900000000001</v>
+        <v>272.9</v>
       </c>
       <c r="H73" t="n">
-        <v>123.69</v>
+        <v>159.19</v>
+      </c>
+      <c r="I73" t="n">
+        <v>376.9</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2480,25 +3222,35 @@
           <t>W01</t>
         </is>
       </c>
-      <c r="B74" t="n">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>W01｜五股1</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>W01</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
         <v>1</v>
       </c>
-      <c r="C74" t="n">
+      <c r="E74" t="n">
         <v>15</v>
       </c>
-      <c r="D74" t="n">
+      <c r="F74" t="n">
         <v>312</v>
       </c>
-      <c r="E74" t="n">
+      <c r="G74" t="n">
         <v>123.77</v>
       </c>
-      <c r="F74" t="n">
+      <c r="H74" t="n">
         <v>72.2</v>
       </c>
-      <c r="G74" t="n">
+      <c r="I74" t="n">
         <v>435.77</v>
       </c>
-      <c r="H74" t="n">
+      <c r="J74" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2508,25 +3260,35 @@
           <t>W01</t>
         </is>
       </c>
-      <c r="B75" t="n">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>W01｜五股1</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>W01</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
         <v>2</v>
       </c>
-      <c r="C75" t="n">
+      <c r="E75" t="n">
         <v>13</v>
       </c>
-      <c r="D75" t="n">
+      <c r="F75" t="n">
         <v>216</v>
       </c>
-      <c r="E75" t="n">
+      <c r="G75" t="n">
         <v>207.02</v>
       </c>
-      <c r="F75" t="n">
+      <c r="H75" t="n">
         <v>120.76</v>
       </c>
-      <c r="G75" t="n">
+      <c r="I75" t="n">
         <v>423.02</v>
       </c>
-      <c r="H75" t="n">
+      <c r="J75" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2536,25 +3298,35 @@
           <t>W01</t>
         </is>
       </c>
-      <c r="B76" t="n">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>W01｜五股1</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>W01</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
         <v>3</v>
       </c>
-      <c r="C76" t="n">
+      <c r="E76" t="n">
         <v>15</v>
       </c>
-      <c r="D76" t="n">
+      <c r="F76" t="n">
         <v>248</v>
       </c>
-      <c r="E76" t="n">
+      <c r="G76" t="n">
         <v>201.41</v>
       </c>
-      <c r="F76" t="n">
+      <c r="H76" t="n">
         <v>117.49</v>
       </c>
-      <c r="G76" t="n">
+      <c r="I76" t="n">
         <v>449.41</v>
       </c>
-      <c r="H76" t="n">
+      <c r="J76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2564,25 +3336,35 @@
           <t>W01</t>
         </is>
       </c>
-      <c r="B77" t="n">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>W01｜五股1</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>W01</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
         <v>4</v>
       </c>
-      <c r="C77" t="n">
-        <v>15</v>
-      </c>
-      <c r="D77" t="n">
-        <v>221</v>
-      </c>
       <c r="E77" t="n">
-        <v>195.74</v>
+        <v>21</v>
       </c>
       <c r="F77" t="n">
-        <v>114.18</v>
+        <v>227</v>
       </c>
       <c r="G77" t="n">
-        <v>416.74</v>
+        <v>202.15</v>
       </c>
       <c r="H77" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="I77" t="n">
+        <v>429.15</v>
+      </c>
+      <c r="J77" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2592,25 +3374,35 @@
           <t>W01</t>
         </is>
       </c>
-      <c r="B78" t="n">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>W01｜五股1</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>W01</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
         <v>5</v>
       </c>
-      <c r="C78" t="n">
+      <c r="E78" t="n">
         <v>15</v>
       </c>
-      <c r="D78" t="n">
+      <c r="F78" t="n">
         <v>200</v>
       </c>
-      <c r="E78" t="n">
+      <c r="G78" t="n">
         <v>157.84</v>
       </c>
-      <c r="F78" t="n">
+      <c r="H78" t="n">
         <v>92.06999999999999</v>
       </c>
-      <c r="G78" t="n">
+      <c r="I78" t="n">
         <v>357.84</v>
       </c>
-      <c r="H78" t="n">
+      <c r="J78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2620,25 +3412,35 @@
           <t>W01</t>
         </is>
       </c>
-      <c r="B79" t="n">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>W01｜五股1</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>W01</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
         <v>6</v>
       </c>
-      <c r="C79" t="n">
-        <v>15</v>
-      </c>
-      <c r="D79" t="n">
+      <c r="E79" t="n">
+        <v>16</v>
+      </c>
+      <c r="F79" t="n">
+        <v>220</v>
+      </c>
+      <c r="G79" t="n">
         <v>219</v>
       </c>
-      <c r="E79" t="n">
-        <v>212.08</v>
-      </c>
-      <c r="F79" t="n">
-        <v>123.71</v>
-      </c>
-      <c r="G79" t="n">
-        <v>431.08</v>
-      </c>
       <c r="H79" t="n">
+        <v>127.75</v>
+      </c>
+      <c r="I79" t="n">
+        <v>439</v>
+      </c>
+      <c r="J79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2648,25 +3450,35 @@
           <t>W02</t>
         </is>
       </c>
-      <c r="B80" t="n">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>W02｜五股2</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>W02</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
         <v>1</v>
       </c>
-      <c r="C80" t="n">
+      <c r="E80" t="n">
         <v>18</v>
       </c>
-      <c r="D80" t="n">
+      <c r="F80" t="n">
         <v>216</v>
       </c>
-      <c r="E80" t="n">
+      <c r="G80" t="n">
         <v>188.55</v>
       </c>
-      <c r="F80" t="n">
+      <c r="H80" t="n">
         <v>109.99</v>
       </c>
-      <c r="G80" t="n">
+      <c r="I80" t="n">
         <v>404.55</v>
       </c>
-      <c r="H80" t="n">
+      <c r="J80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2676,25 +3488,35 @@
           <t>W02</t>
         </is>
       </c>
-      <c r="B81" t="n">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>W02｜五股2</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>W02</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
         <v>2</v>
       </c>
-      <c r="C81" t="n">
+      <c r="E81" t="n">
         <v>19</v>
       </c>
-      <c r="D81" t="n">
+      <c r="F81" t="n">
         <v>208</v>
       </c>
-      <c r="E81" t="n">
+      <c r="G81" t="n">
         <v>153.83</v>
       </c>
-      <c r="F81" t="n">
+      <c r="H81" t="n">
         <v>89.73</v>
       </c>
-      <c r="G81" t="n">
+      <c r="I81" t="n">
         <v>361.83</v>
       </c>
-      <c r="H81" t="n">
+      <c r="J81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2704,25 +3526,35 @@
           <t>W02</t>
         </is>
       </c>
-      <c r="B82" t="n">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>W02｜五股2</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>W02</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
         <v>3</v>
       </c>
-      <c r="C82" t="n">
+      <c r="E82" t="n">
         <v>18</v>
       </c>
-      <c r="D82" t="n">
+      <c r="F82" t="n">
         <v>216</v>
       </c>
-      <c r="E82" t="n">
+      <c r="G82" t="n">
         <v>160.36</v>
       </c>
-      <c r="F82" t="n">
+      <c r="H82" t="n">
         <v>93.55</v>
       </c>
-      <c r="G82" t="n">
+      <c r="I82" t="n">
         <v>376.36</v>
       </c>
-      <c r="H82" t="n">
+      <c r="J82" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2732,25 +3564,35 @@
           <t>W02</t>
         </is>
       </c>
-      <c r="B83" t="n">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>W02｜五股2</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>W02</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
         <v>4</v>
       </c>
-      <c r="C83" t="n">
+      <c r="E83" t="n">
         <v>16</v>
       </c>
-      <c r="D83" t="n">
+      <c r="F83" t="n">
         <v>190</v>
       </c>
-      <c r="E83" t="n">
+      <c r="G83" t="n">
         <v>199.42</v>
       </c>
-      <c r="F83" t="n">
+      <c r="H83" t="n">
         <v>116.33</v>
       </c>
-      <c r="G83" t="n">
+      <c r="I83" t="n">
         <v>389.42</v>
       </c>
-      <c r="H83" t="n">
+      <c r="J83" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2760,25 +3602,35 @@
           <t>W02</t>
         </is>
       </c>
-      <c r="B84" t="n">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>W02｜五股2</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>W02</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
         <v>5</v>
       </c>
-      <c r="C84" t="n">
+      <c r="E84" t="n">
         <v>24</v>
       </c>
-      <c r="D84" t="n">
+      <c r="F84" t="n">
         <v>192</v>
       </c>
-      <c r="E84" t="n">
+      <c r="G84" t="n">
         <v>198.01</v>
       </c>
-      <c r="F84" t="n">
+      <c r="H84" t="n">
         <v>115.5</v>
       </c>
-      <c r="G84" t="n">
+      <c r="I84" t="n">
         <v>390.01</v>
       </c>
-      <c r="H84" t="n">
+      <c r="J84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2788,25 +3640,35 @@
           <t>W02</t>
         </is>
       </c>
-      <c r="B85" t="n">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>W02｜五股2</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>W02</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
         <v>6</v>
       </c>
-      <c r="C85" t="n">
+      <c r="E85" t="n">
         <v>23</v>
       </c>
-      <c r="D85" t="n">
+      <c r="F85" t="n">
         <v>184</v>
       </c>
-      <c r="E85" t="n">
+      <c r="G85" t="n">
         <v>219.6</v>
       </c>
-      <c r="F85" t="n">
+      <c r="H85" t="n">
         <v>128.1</v>
       </c>
-      <c r="G85" t="n">
+      <c r="I85" t="n">
         <v>403.6</v>
       </c>
-      <c r="H85" t="n">
+      <c r="J85" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/Daily_Route_Summary_compact.xlsx
+++ b/output/Daily_Route_Summary_compact.xlsx
@@ -3350,19 +3350,19 @@
         <v>4</v>
       </c>
       <c r="E77" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F77" t="n">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="G77" t="n">
-        <v>202.15</v>
+        <v>195.74</v>
       </c>
       <c r="H77" t="n">
-        <v>117.92</v>
+        <v>114.18</v>
       </c>
       <c r="I77" t="n">
-        <v>429.15</v>
+        <v>416.74</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -3426,19 +3426,19 @@
         <v>6</v>
       </c>
       <c r="E79" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F79" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G79" t="n">
-        <v>219</v>
+        <v>212.08</v>
       </c>
       <c r="H79" t="n">
-        <v>127.75</v>
+        <v>123.71</v>
       </c>
       <c r="I79" t="n">
-        <v>439</v>
+        <v>431.08</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>

--- a/output/Daily_Route_Summary_compact.xlsx
+++ b/output/Daily_Route_Summary_compact.xlsx
@@ -3350,19 +3350,19 @@
         <v>4</v>
       </c>
       <c r="E77" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F77" t="n">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="G77" t="n">
-        <v>195.74</v>
+        <v>202.15</v>
       </c>
       <c r="H77" t="n">
-        <v>114.18</v>
+        <v>117.92</v>
       </c>
       <c r="I77" t="n">
-        <v>416.74</v>
+        <v>429.15</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -3426,19 +3426,19 @@
         <v>6</v>
       </c>
       <c r="E79" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F79" t="n">
+        <v>220</v>
+      </c>
+      <c r="G79" t="n">
         <v>219</v>
       </c>
-      <c r="G79" t="n">
-        <v>212.08</v>
-      </c>
       <c r="H79" t="n">
-        <v>123.71</v>
+        <v>127.75</v>
       </c>
       <c r="I79" t="n">
-        <v>431.08</v>
+        <v>439</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
